--- a/tests/traces/mi300/facebook_timesformer-base-finetuned-k400__1016002_perf_report.xlsx
+++ b/tests/traces/mi300/facebook_timesformer-base-finetuned-k400__1016002_perf_report.xlsx
@@ -1,22 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gpu_timeline" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ops_summary_by_category" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ops_summary" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ops_unique_args" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unified_perf_summary" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GEMM" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONV_fwd" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BinaryElementwise" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UnaryElementwise" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Normalization" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="gpu_timeline" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ops_summary_by_category" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ops_summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="ops_unique_args" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="unified_perf_summary" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="GEMM" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="CONV_fwd" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="BinaryElementwise" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="UnaryElementwise" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Normalization" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Reduce_fwd" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="kernel_summary" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="short_kernel_histogram" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="short_kernels_summary" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1739,6 +1743,3024 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AJ2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>param: num_input_elems</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>param: num_output_elems</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>param: dtype_in_out</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>param: reduce_type</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>GFLOPS_first</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Data Moved (MB)_first</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>FLOPS/Byte_first</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>TB/s_mean</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>TB/s_median</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>TB/s_std</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>TB/s_min</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>TB/s_max</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>TFLOPS/s_mean</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>TFLOPS/s_median</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>TFLOPS/s_std</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>TFLOPS/s_min</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>TFLOPS/s_max</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>process_name_first</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>process_label_first</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>thread_name_first</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Compute Spec</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>kernel_details__summarize_kernel_stats</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>trunc_kernel_details</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Input Dims_first</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Input type_first</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Input Strides_first</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Concrete Inputs_first</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_mean</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_median</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_std</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_min</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_max</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_sum</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>name_count</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>UID_first</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>aten::mean</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>6144</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>('c10::BFloat16', None)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>6.144e-06</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.01172065734863281</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.4999186330349878</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.001553891225457198</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.001580429492605539</v>
+      </c>
+      <c r="K2" t="n">
+        <v>7.402240095894243e-05</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.001356503368364322</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.001622191286414024</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.0007768191773156245</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.0007900861515515403</v>
+      </c>
+      <c r="P2" t="n">
+        <v>3.700517750136228e-05</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.0006781413096200486</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.0008109636504253674</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>thread 13201 (python3)</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>vector_bf16</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;128, 4, at::native::ReduceOp&lt;c10::BFloat16, at::native::MeanOps&lt;c10::BFloat16, float, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::MeanOps&lt;c10::BFloat16, float, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt;)', 'stream': 0, 'count': 12, 'total_duration_us': np.float64(95.12499999999999), 'mean_duration_us': np.float64(7.927083333333332), 'median_duration_us': np.float64(7.7765), 'std_dev_duration_us': np.float64(0.39327184371062673), 'min_duration_us': np.float64(7.576), 'max_duration_us': np.float64(9.06)}]</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;128, 4, at::native::ReduceOp&lt;c10:...', 'stream': 0, 'mean_duration_us': np.float64(7.93)}]</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>[[1, 8, 768], [], [], []]</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>['c10::BFloat16', 'ScalarList', 'Scalar', '']</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>[[19273728, 2409216, 1], [], [], []]</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>['', '[1]', 'True', '']</t>
+        </is>
+      </c>
+      <c r="AC2" t="n">
+        <v>7.927083333333333</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>7.7763671875</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.4107497551951304</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>7.576171875</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>9.06005859375</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>95.125</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>312</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Parent op category</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Parent cpu_op</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel stream</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel duration (µs)_sum</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel duration (µs)_count</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel duration (µs)_mean</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel duration (µs)_min</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel duration (µs)_max</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Percent of kernels time (%)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Percent of total time (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>aten::_softmax</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>void at::native::(anonymous namespace)::cunn_SoftMaxForwardReg&lt;c10::BFloat16, float, c10::BFloat16, at::native::(anonymous namespace)::SoftMaxForwardEpilogue, long, 4&gt;(c10::BFloat16*, c10::BFloat16 const*, long)</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>41722.677</v>
+      </c>
+      <c r="F2" t="n">
+        <v>12</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3476.88975</v>
+      </c>
+      <c r="H2" t="n">
+        <v>3406.829</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3656.282</v>
+      </c>
+      <c r="J2" t="n">
+        <v>35.1322551914681</v>
+      </c>
+      <c r="K2" t="n">
+        <v>34.40557346820402</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>aten::bmm</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT128x256x32_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB4_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA1024_LBSPPB256_LBSPPM0_LPA0_LPB4_LPM0_LRVW4_LWPMn1_MIAV0_MIWT8_4_MO40_NTn1_NTA0_NTB0_NTC0_NTD4_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW8_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA8_VWB4_WSGRA0_WSGRB0_WS64_WG16_16_1</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>14545.618</v>
+      </c>
+      <c r="F3" t="n">
+        <v>12</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1212.134833333333</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1191.738</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1232.471</v>
+      </c>
+      <c r="J3" t="n">
+        <v>12.24802434162151</v>
+      </c>
+      <c r="K3" t="n">
+        <v>11.99468405968847</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>aten::bmm</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x448x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA2_GRVWB2_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA128_LBSPPB128_LBSPPM0_LPA16_LPB4_LPM0_LRVW4_LWPMn1_MIAV0_MIWT1_7_MO40_NTn1_NTA0_NTB4_NTC0_NTD4_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_16_1</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>13710.098</v>
+      </c>
+      <c r="F4" t="n">
+        <v>12</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1142.508166666667</v>
+      </c>
+      <c r="H4" t="n">
+        <v>876.333</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1221.767</v>
+      </c>
+      <c r="J4" t="n">
+        <v>11.54448123345576</v>
+      </c>
+      <c r="K4" t="n">
+        <v>11.30569316046708</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>aten::mul</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;8, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>11023.792</v>
+      </c>
+      <c r="F5" t="n">
+        <v>24</v>
+      </c>
+      <c r="G5" t="n">
+        <v>459.3246666666666</v>
+      </c>
+      <c r="H5" t="n">
+        <v>5.011</v>
+      </c>
+      <c r="I5" t="n">
+        <v>919.793</v>
+      </c>
+      <c r="J5" t="n">
+        <v>9.282498189693451</v>
+      </c>
+      <c r="K5" t="n">
+        <v>9.090497370391638</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>aten::bmm</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT64x224x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA1024_LBSPPB128_LBSPPM0_LPA32_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT2_7_MO40_NTn1_NTA0_NTB4_NTC0_NTD4_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW2_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA2_VWB1_WSGRA0_WSGRB0_WS64_WG32_8_1</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>9716.842000000001</v>
+      </c>
+      <c r="F6" t="n">
+        <v>12</v>
+      </c>
+      <c r="G6" t="n">
+        <v>809.7368333333334</v>
+      </c>
+      <c r="H6" t="n">
+        <v>804.769</v>
+      </c>
+      <c r="I6" t="n">
+        <v>817.117</v>
+      </c>
+      <c r="J6" t="n">
+        <v>8.18199112197847</v>
+      </c>
+      <c r="K6" t="n">
+        <v>8.012753383727762</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>aten::copy_</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5046.197</v>
+      </c>
+      <c r="F7" t="n">
+        <v>122</v>
+      </c>
+      <c r="G7" t="n">
+        <v>41.36227049180328</v>
+      </c>
+      <c r="H7" t="n">
+        <v>4.289</v>
+      </c>
+      <c r="I7" t="n">
+        <v>167.624</v>
+      </c>
+      <c r="J7" t="n">
+        <v>4.249110879208944</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4.161221525132022</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x192x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA1024_LBSPPB256_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT8_6_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW8_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA8_VWB2_WSGRA0_WSGRB0_WS64_WG32_8_1</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>4551.276</v>
+      </c>
+      <c r="F8" t="n">
+        <v>24</v>
+      </c>
+      <c r="G8" t="n">
+        <v>189.6365</v>
+      </c>
+      <c r="H8" t="n">
+        <v>179.051</v>
+      </c>
+      <c r="I8" t="n">
+        <v>202.905</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.832366506080235</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.753097165651036</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>aten::bmm</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x16x32_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB2_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA2048_LBSPPB128_LBSPPM0_LPA0_LPB4_LPM0_LRVW4_LWPMn1_MIAV0_MIWT4_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD4_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW4_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA4_VWB1_WSGRA0_WSGRB0_WS64_WG64_4_1</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3356.223</v>
+      </c>
+      <c r="F9" t="n">
+        <v>12</v>
+      </c>
+      <c r="G9" t="n">
+        <v>279.68525</v>
+      </c>
+      <c r="H9" t="n">
+        <v>246.526</v>
+      </c>
+      <c r="I9" t="n">
+        <v>310.312</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.826081435653677</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.767626271971381</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x224x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA2_GRVWB2_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA1024_LBSPPB128_LBSPPM0_LPA4_LPB4_LPM0_LRVW4_LWPMn1_MIAV0_MIWT8_7_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW8_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA8_VWB1_WSGRA0_WSGRB0_WS64_WG32_8_1</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3057.256</v>
+      </c>
+      <c r="F10" t="n">
+        <v>12</v>
+      </c>
+      <c r="G10" t="n">
+        <v>254.7713333333333</v>
+      </c>
+      <c r="H10" t="n">
+        <v>250.615</v>
+      </c>
+      <c r="I10" t="n">
+        <v>262.162</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.574338601946539</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.521090531154258</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x128x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA1024_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT8_4_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW8_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA8_VWB4_WSGRA0_WSGRB0_WS64_WG32_8_1</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2600.847</v>
+      </c>
+      <c r="F11" t="n">
+        <v>12</v>
+      </c>
+      <c r="G11" t="n">
+        <v>216.73725</v>
+      </c>
+      <c r="H11" t="n">
+        <v>205.03</v>
+      </c>
+      <c r="I11" t="n">
+        <v>222.872</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.190022958449292</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.144724139777944</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x128x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB1024_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT4_8_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW4_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA4_VWB8_WSGRA0_WSGRB0_WS64_WG64_4_1</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2596.131</v>
+      </c>
+      <c r="F12" t="n">
+        <v>36</v>
+      </c>
+      <c r="G12" t="n">
+        <v>72.11475</v>
+      </c>
+      <c r="H12" t="n">
+        <v>66.512</v>
+      </c>
+      <c r="I12" t="n">
+        <v>78.86</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.186051887382041</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.140835207040573</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>NORM_fwd</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>aten::native_layer_norm</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2300.166</v>
+      </c>
+      <c r="F13" t="n">
+        <v>37</v>
+      </c>
+      <c r="G13" t="n">
+        <v>62.16664864864865</v>
+      </c>
+      <c r="H13" t="n">
+        <v>55.326</v>
+      </c>
+      <c r="I13" t="n">
+        <v>69.599</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.936836864392437</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.896774991261106</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>aten::gelu</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;8, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1209.566</v>
+      </c>
+      <c r="F14" t="n">
+        <v>12</v>
+      </c>
+      <c r="G14" t="n">
+        <v>100.7971666666667</v>
+      </c>
+      <c r="H14" t="n">
+        <v>96.38</v>
+      </c>
+      <c r="I14" t="n">
+        <v>107.646</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.01850562903534</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.9974386801125359</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>aten::add</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1013.612</v>
+      </c>
+      <c r="F15" t="n">
+        <v>36</v>
+      </c>
+      <c r="G15" t="n">
+        <v>28.15588888888889</v>
+      </c>
+      <c r="H15" t="n">
+        <v>24.976</v>
+      </c>
+      <c r="I15" t="n">
+        <v>32.995</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.8535040896137696</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.8358500614486748</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>aten::cat</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>void at::native::(anonymous namespace)::CatArrayBatchedCopy_contig&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 3, 128, 1&gt;(at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;*, at::native::(anonymous namespace)::CatArrInputTensorMetadata&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 128, 1&gt;, at::native::(anonymous namespace)::TensorSizeStride&lt;unsigned int, 4u&gt;, int, unsigned int)</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>875.427</v>
+      </c>
+      <c r="F16" t="n">
+        <v>25</v>
+      </c>
+      <c r="G16" t="n">
+        <v>35.01708</v>
+      </c>
+      <c r="H16" t="n">
+        <v>30.349</v>
+      </c>
+      <c r="I16" t="n">
+        <v>39.65</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.7371464866816035</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.7218992195670819</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>aten::cat</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 3, 64, 64&gt;(at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;*, at::native::(anonymous namespace)::CatArrInputTensorMetadata&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 64, 64&gt;, at::native::(anonymous namespace)::TensorSizeStride&lt;unsigned int, 4u&gt;, int, unsigned int)</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>653.008</v>
+      </c>
+      <c r="F17" t="n">
+        <v>13</v>
+      </c>
+      <c r="G17" t="n">
+        <v>50.23138461538462</v>
+      </c>
+      <c r="H17" t="n">
+        <v>44.02</v>
+      </c>
+      <c r="I17" t="n">
+        <v>101.111</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.5498603001449357</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.5384868933344082</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CONV_fwd</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>aten::miopen_convolution</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>igemm_fwd_gtcx3_nhwc_bf16_bx0_ex1_bt256x64x8_wt64x16x4_ws1x1_wr2x2_ta1x1x8x1_1x8x1x32_tb1x1x2x1_1x8x1x32_me</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>246.806</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="n">
+        <v>246.806</v>
+      </c>
+      <c r="H18" t="n">
+        <v>246.806</v>
+      </c>
+      <c r="I18" t="n">
+        <v>246.806</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.2078210699372305</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.2035224625062663</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>aten::add</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int, bool)#1})</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>151.547</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" t="n">
+        <v>75.7735</v>
+      </c>
+      <c r="H19" t="n">
+        <v>29.788</v>
+      </c>
+      <c r="I19" t="n">
+        <v>121.759</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.1276089709560443</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.124969484637477</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>aten::_softmax</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>void (anonymous namespace)::softmax_warp_forward&lt;c10::BFloat16, c10::BFloat16, float, 3, false, false&gt;(c10::BFloat16*, c10::BFloat16 const*, int, int, int, bool const*, int, bool)</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>133.974</v>
+      </c>
+      <c r="F20" t="n">
+        <v>12</v>
+      </c>
+      <c r="G20" t="n">
+        <v>11.1645</v>
+      </c>
+      <c r="H20" t="n">
+        <v>9.34</v>
+      </c>
+      <c r="I20" t="n">
+        <v>12.227</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.1128117631814887</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.1104783449017225</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>reduce</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>aten::mean</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>void at::native::reduce_kernel&lt;128, 4, at::native::ReduceOp&lt;c10::BFloat16, at::native::MeanOps&lt;c10::BFloat16, float, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::MeanOps&lt;c10::BFloat16, float, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt;)</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>95.125</v>
+      </c>
+      <c r="F21" t="n">
+        <v>12</v>
+      </c>
+      <c r="G21" t="n">
+        <v>7.927083333333333</v>
+      </c>
+      <c r="H21" t="n">
+        <v>7.576</v>
+      </c>
+      <c r="I21" t="n">
+        <v>9.06</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.0800992653249072</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.07844247808363081</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>aten::add_</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int, bool)#1})</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>51.999</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" t="n">
+        <v>51.999</v>
+      </c>
+      <c r="H22" t="n">
+        <v>51.999</v>
+      </c>
+      <c r="I22" t="n">
+        <v>51.999</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.04378535293171984</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.04287968901835184</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CONV_fwd</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>aten::miopen_convolution</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>batched_transpose_256x4_half</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>33.917</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="n">
+        <v>33.917</v>
+      </c>
+      <c r="H23" t="n">
+        <v>33.917</v>
+      </c>
+      <c r="I23" t="n">
+        <v>33.917</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.02855954567174642</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.02796881502404737</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>CONV_fwd</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>aten::miopen_convolution</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>batched_transpose_32x16_half</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>32.032</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="n">
+        <v>32.032</v>
+      </c>
+      <c r="H24" t="n">
+        <v>32.032</v>
+      </c>
+      <c r="I24" t="n">
+        <v>32.032</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.02697229610394142</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.02641439640446635</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>CONV_fwd</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>aten::miopen_convolution</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>SubTensorOpWithScalar1d</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>16.396</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" t="n">
+        <v>16.396</v>
+      </c>
+      <c r="H25" t="n">
+        <v>16.396</v>
+      </c>
+      <c r="I25" t="n">
+        <v>16.396</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.01380612409216482</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.01352055580193651</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMBSK_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD0_NTM0_NEPBS0_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>9.260999999999999</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" t="n">
+        <v>9.260999999999999</v>
+      </c>
+      <c r="H26" t="n">
+        <v>9.260999999999999</v>
+      </c>
+      <c r="I26" t="n">
+        <v>9.260999999999999</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.007798152916414881</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.007636854554875215</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>CONV_fwd</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>aten::miopen_convolution</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>batched_transpose_128x4_half</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>4.891</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" t="n">
+        <v>4.891</v>
+      </c>
+      <c r="H27" t="n">
+        <v>4.891</v>
+      </c>
+      <c r="I27" t="n">
+        <v>4.891</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.004118428454182614</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.004033242158286867</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>aten::upsample_nearest1d</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>void at::native::(anonymous namespace)::upsample_nearest1d_out_frame&lt;c10::BFloat16, &amp;at::native::nearest_neighbor_compute_source_index&gt;(c10::BFloat16 const*, unsigned long, unsigned long, unsigned long, unsigned long, c10::BFloat16*, float)</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>4.208</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" t="n">
+        <v>4.208</v>
+      </c>
+      <c r="H28" t="n">
+        <v>4.208</v>
+      </c>
+      <c r="I28" t="n">
+        <v>4.208</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.003543313624044252</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.003470023104083242</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C101"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>bin_start</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>bin_end</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>4.208</v>
+      </c>
+      <c r="B2" t="n">
+        <v>4.25932</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>4.25932</v>
+      </c>
+      <c r="B3" t="n">
+        <v>4.31064</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.31064</v>
+      </c>
+      <c r="B4" t="n">
+        <v>4.36196</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4.36196</v>
+      </c>
+      <c r="B5" t="n">
+        <v>4.41328</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4.41328</v>
+      </c>
+      <c r="B6" t="n">
+        <v>4.4646</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>4.4646</v>
+      </c>
+      <c r="B7" t="n">
+        <v>4.51592</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>4.51592</v>
+      </c>
+      <c r="B8" t="n">
+        <v>4.56724</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>4.56724</v>
+      </c>
+      <c r="B9" t="n">
+        <v>4.61856</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>4.61856</v>
+      </c>
+      <c r="B10" t="n">
+        <v>4.66988</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>4.66988</v>
+      </c>
+      <c r="B11" t="n">
+        <v>4.721200000000001</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>4.721200000000001</v>
+      </c>
+      <c r="B12" t="n">
+        <v>4.77252</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>4.77252</v>
+      </c>
+      <c r="B13" t="n">
+        <v>4.823840000000001</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.823840000000001</v>
+      </c>
+      <c r="B14" t="n">
+        <v>4.87516</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>4.87516</v>
+      </c>
+      <c r="B15" t="n">
+        <v>4.92648</v>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>4.92648</v>
+      </c>
+      <c r="B16" t="n">
+        <v>4.9778</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>4.9778</v>
+      </c>
+      <c r="B17" t="n">
+        <v>5.02912</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>5.02912</v>
+      </c>
+      <c r="B18" t="n">
+        <v>5.08044</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>5.08044</v>
+      </c>
+      <c r="B19" t="n">
+        <v>5.13176</v>
+      </c>
+      <c r="C19" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>5.13176</v>
+      </c>
+      <c r="B20" t="n">
+        <v>5.18308</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>5.18308</v>
+      </c>
+      <c r="B21" t="n">
+        <v>5.2344</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>5.2344</v>
+      </c>
+      <c r="B22" t="n">
+        <v>5.28572</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>5.28572</v>
+      </c>
+      <c r="B23" t="n">
+        <v>5.33704</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>5.33704</v>
+      </c>
+      <c r="B24" t="n">
+        <v>5.38836</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>5.38836</v>
+      </c>
+      <c r="B25" t="n">
+        <v>5.43968</v>
+      </c>
+      <c r="C25" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.43968</v>
+      </c>
+      <c r="B26" t="n">
+        <v>5.491</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>5.491</v>
+      </c>
+      <c r="B27" t="n">
+        <v>5.54232</v>
+      </c>
+      <c r="C27" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>5.54232</v>
+      </c>
+      <c r="B28" t="n">
+        <v>5.593640000000001</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>5.593640000000001</v>
+      </c>
+      <c r="B29" t="n">
+        <v>5.64496</v>
+      </c>
+      <c r="C29" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>5.64496</v>
+      </c>
+      <c r="B30" t="n">
+        <v>5.69628</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>5.69628</v>
+      </c>
+      <c r="B31" t="n">
+        <v>5.7476</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>5.7476</v>
+      </c>
+      <c r="B32" t="n">
+        <v>5.79892</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>5.79892</v>
+      </c>
+      <c r="B33" t="n">
+        <v>5.85024</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>5.85024</v>
+      </c>
+      <c r="B34" t="n">
+        <v>5.90156</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>5.90156</v>
+      </c>
+      <c r="B35" t="n">
+        <v>5.95288</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>5.95288</v>
+      </c>
+      <c r="B36" t="n">
+        <v>6.0042</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>6.0042</v>
+      </c>
+      <c r="B37" t="n">
+        <v>6.05552</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>6.05552</v>
+      </c>
+      <c r="B38" t="n">
+        <v>6.10684</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>6.10684</v>
+      </c>
+      <c r="B39" t="n">
+        <v>6.158160000000001</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>6.158160000000001</v>
+      </c>
+      <c r="B40" t="n">
+        <v>6.20948</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>6.20948</v>
+      </c>
+      <c r="B41" t="n">
+        <v>6.2608</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>6.2608</v>
+      </c>
+      <c r="B42" t="n">
+        <v>6.31212</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>6.31212</v>
+      </c>
+      <c r="B43" t="n">
+        <v>6.363440000000001</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>6.363440000000001</v>
+      </c>
+      <c r="B44" t="n">
+        <v>6.41476</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>6.41476</v>
+      </c>
+      <c r="B45" t="n">
+        <v>6.46608</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>6.46608</v>
+      </c>
+      <c r="B46" t="n">
+        <v>6.5174</v>
+      </c>
+      <c r="C46" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>6.5174</v>
+      </c>
+      <c r="B47" t="n">
+        <v>6.56872</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>6.56872</v>
+      </c>
+      <c r="B48" t="n">
+        <v>6.620039999999999</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>6.620039999999999</v>
+      </c>
+      <c r="B49" t="n">
+        <v>6.67136</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>6.67136</v>
+      </c>
+      <c r="B50" t="n">
+        <v>6.72268</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>6.72268</v>
+      </c>
+      <c r="B51" t="n">
+        <v>6.774</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>6.774</v>
+      </c>
+      <c r="B52" t="n">
+        <v>6.82532</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>6.82532</v>
+      </c>
+      <c r="B53" t="n">
+        <v>6.87664</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>6.87664</v>
+      </c>
+      <c r="B54" t="n">
+        <v>6.927960000000001</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>6.927960000000001</v>
+      </c>
+      <c r="B55" t="n">
+        <v>6.97928</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>6.97928</v>
+      </c>
+      <c r="B56" t="n">
+        <v>7.0306</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>7.0306</v>
+      </c>
+      <c r="B57" t="n">
+        <v>7.08192</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>7.08192</v>
+      </c>
+      <c r="B58" t="n">
+        <v>7.133240000000001</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>7.133240000000001</v>
+      </c>
+      <c r="B59" t="n">
+        <v>7.184559999999999</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>7.184559999999999</v>
+      </c>
+      <c r="B60" t="n">
+        <v>7.23588</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>7.23588</v>
+      </c>
+      <c r="B61" t="n">
+        <v>7.2872</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>7.2872</v>
+      </c>
+      <c r="B62" t="n">
+        <v>7.33852</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>7.33852</v>
+      </c>
+      <c r="B63" t="n">
+        <v>7.38984</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>7.38984</v>
+      </c>
+      <c r="B64" t="n">
+        <v>7.44116</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>7.44116</v>
+      </c>
+      <c r="B65" t="n">
+        <v>7.49248</v>
+      </c>
+      <c r="C65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>7.49248</v>
+      </c>
+      <c r="B66" t="n">
+        <v>7.5438</v>
+      </c>
+      <c r="C66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>7.5438</v>
+      </c>
+      <c r="B67" t="n">
+        <v>7.59512</v>
+      </c>
+      <c r="C67" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>7.59512</v>
+      </c>
+      <c r="B68" t="n">
+        <v>7.64644</v>
+      </c>
+      <c r="C68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>7.64644</v>
+      </c>
+      <c r="B69" t="n">
+        <v>7.697760000000001</v>
+      </c>
+      <c r="C69" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>7.697760000000001</v>
+      </c>
+      <c r="B70" t="n">
+        <v>7.74908</v>
+      </c>
+      <c r="C70" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>7.74908</v>
+      </c>
+      <c r="B71" t="n">
+        <v>7.8004</v>
+      </c>
+      <c r="C71" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>7.8004</v>
+      </c>
+      <c r="B72" t="n">
+        <v>7.85172</v>
+      </c>
+      <c r="C72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>7.85172</v>
+      </c>
+      <c r="B73" t="n">
+        <v>7.90304</v>
+      </c>
+      <c r="C73" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>7.90304</v>
+      </c>
+      <c r="B74" t="n">
+        <v>7.954359999999999</v>
+      </c>
+      <c r="C74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>7.954359999999999</v>
+      </c>
+      <c r="B75" t="n">
+        <v>8.00568</v>
+      </c>
+      <c r="C75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>8.00568</v>
+      </c>
+      <c r="B76" t="n">
+        <v>8.057</v>
+      </c>
+      <c r="C76" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>8.057</v>
+      </c>
+      <c r="B77" t="n">
+        <v>8.108319999999999</v>
+      </c>
+      <c r="C77" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>8.108319999999999</v>
+      </c>
+      <c r="B78" t="n">
+        <v>8.15964</v>
+      </c>
+      <c r="C78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>8.15964</v>
+      </c>
+      <c r="B79" t="n">
+        <v>8.21096</v>
+      </c>
+      <c r="C79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>8.21096</v>
+      </c>
+      <c r="B80" t="n">
+        <v>8.262280000000001</v>
+      </c>
+      <c r="C80" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>8.262280000000001</v>
+      </c>
+      <c r="B81" t="n">
+        <v>8.313600000000001</v>
+      </c>
+      <c r="C81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>8.313600000000001</v>
+      </c>
+      <c r="B82" t="n">
+        <v>8.36492</v>
+      </c>
+      <c r="C82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>8.36492</v>
+      </c>
+      <c r="B83" t="n">
+        <v>8.41624</v>
+      </c>
+      <c r="C83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>8.41624</v>
+      </c>
+      <c r="B84" t="n">
+        <v>8.467559999999999</v>
+      </c>
+      <c r="C84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>8.467559999999999</v>
+      </c>
+      <c r="B85" t="n">
+        <v>8.518879999999999</v>
+      </c>
+      <c r="C85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>8.518879999999999</v>
+      </c>
+      <c r="B86" t="n">
+        <v>8.5702</v>
+      </c>
+      <c r="C86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>8.5702</v>
+      </c>
+      <c r="B87" t="n">
+        <v>8.62152</v>
+      </c>
+      <c r="C87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>8.62152</v>
+      </c>
+      <c r="B88" t="n">
+        <v>8.672840000000001</v>
+      </c>
+      <c r="C88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>8.672840000000001</v>
+      </c>
+      <c r="B89" t="n">
+        <v>8.724160000000001</v>
+      </c>
+      <c r="C89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>8.724160000000001</v>
+      </c>
+      <c r="B90" t="n">
+        <v>8.77548</v>
+      </c>
+      <c r="C90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>8.77548</v>
+      </c>
+      <c r="B91" t="n">
+        <v>8.826799999999999</v>
+      </c>
+      <c r="C91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>8.826799999999999</v>
+      </c>
+      <c r="B92" t="n">
+        <v>8.878119999999999</v>
+      </c>
+      <c r="C92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>8.878119999999999</v>
+      </c>
+      <c r="B93" t="n">
+        <v>8.92944</v>
+      </c>
+      <c r="C93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>8.92944</v>
+      </c>
+      <c r="B94" t="n">
+        <v>8.98076</v>
+      </c>
+      <c r="C94" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>8.98076</v>
+      </c>
+      <c r="B95" t="n">
+        <v>9.032080000000001</v>
+      </c>
+      <c r="C95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>9.032080000000001</v>
+      </c>
+      <c r="B96" t="n">
+        <v>9.083400000000001</v>
+      </c>
+      <c r="C96" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>9.083400000000001</v>
+      </c>
+      <c r="B97" t="n">
+        <v>9.13472</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>9.13472</v>
+      </c>
+      <c r="B98" t="n">
+        <v>9.18604</v>
+      </c>
+      <c r="C98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>9.18604</v>
+      </c>
+      <c r="B99" t="n">
+        <v>9.237359999999999</v>
+      </c>
+      <c r="C99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>9.237359999999999</v>
+      </c>
+      <c r="B100" t="n">
+        <v>9.288679999999999</v>
+      </c>
+      <c r="C100" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>9.288679999999999</v>
+      </c>
+      <c r="B101" t="n">
+        <v>9.34</v>
+      </c>
+      <c r="C101" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Parent cpu_op</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Input dims</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Input strides</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Concrete Inputs</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel name</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Short Kernel duration (µs) sum</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Short Kernel count</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Short Kernel duration (µs) mean</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Short Kernel duration (µs) percent of total time</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>aten::mean</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>((1, 8, 768), (), (), ())</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>((19273728, 2409216, 1), (), (), ())</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>('', '[1]', 'True', '')</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>void at::native::reduce_kernel&lt;128, 4, at::native::ReduceOp&lt;c10::BFloat16, at::native::MeanOps&lt;c10::BFloat16, float, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::MeanOps&lt;c10::BFloat16, float, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt;)</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>95.125</v>
+      </c>
+      <c r="G2" t="n">
+        <v>12</v>
+      </c>
+      <c r="H2" t="n">
+        <v>7.927083333333333</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.07844247808363081</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>aten::mul</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>((3136, 12, 8, 8), ())</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>((768, 64, 8, 1), ())</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;8, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>65.258</v>
+      </c>
+      <c r="G3" t="n">
+        <v>12</v>
+      </c>
+      <c r="H3" t="n">
+        <v>5.438166666666667</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.05381339537221107</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>aten::copy_</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>((1, 8, 1, 1, 1, 768), (1, 8, 1, 1, 1, 768), ())</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>((6144, 768, 768, 6144, 768, 1), (0, 0, 19268352, 19268352, 768, 1), ())</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>('', '', 'False')</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>59.084</v>
+      </c>
+      <c r="G4" t="n">
+        <v>12</v>
+      </c>
+      <c r="H4" t="n">
+        <v>4.923666666666667</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.04872215900229428</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>aten::_softmax</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>((3136, 12, 8, 8), (), ())</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>((768, 64, 8, 1), (), ())</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>('', '-1', 'False')</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>void (anonymous namespace)::softmax_warp_forward&lt;c10::BFloat16, c10::BFloat16, float, 3, false, false&gt;(c10::BFloat16*, c10::BFloat16 const*, int, int, int, bool const*, int, bool)</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>9.34</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>9.34</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.007701999950603014</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>((400,), (1, 768), (768, 400), (), ())</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>((1,), (19268352, 1), (1, 768), (), ())</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>('', '', '', '1', '1')</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMBSK_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD0_NTM0_NEPBS0_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>9.260999999999999</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>9.260999999999999</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.007636854554875215</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>aten::copy_</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>((1, 768, 8), (1, 768, 8), ())</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>((6144, 8, 1), (6144, 1, 768), ())</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>('', '', 'False')</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>6.494</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>6.494</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.005355116453877513</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>aten::miopen_convolution</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>((128, 3, 224, 224), (768, 3, 16, 16), (768,), (), (), (), (), (), ())</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>((150528, 50176, 224, 1), (768, 256, 16, 1), (1,), (), (), (), (), (), ())</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>('', '', '', '[0, 0]', '[16, 16]', '[1, 1]', '1', 'False', 'False')</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>batched_transpose_128x4_half</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>4.891</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>4.891</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.004033242158286867</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>aten::upsample_nearest1d</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>((1, 768, 8), (), ())</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>((6144, 1, 768), (), ())</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>('', '[128]', '')</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>void at::native::(anonymous namespace)::upsample_nearest1d_out_frame&lt;c10::BFloat16, &amp;at::native::nearest_neighbor_compute_source_index&gt;(c10::BFloat16 const*, unsigned long, unsigned long, unsigned long, unsigned long, c10::BFloat16*, float)</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>4.208</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4.208</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.003470023104083242</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -12309,14 +15331,32 @@
       <c r="N35" t="n">
         <v>4.775930377392134</v>
       </c>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
+      <c r="O35" t="n">
+        <v>6.144e-06</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0.01172065734863281</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0.4999186330349878</v>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>vector_bf16</t>
+        </is>
+      </c>
+      <c r="S35" t="n">
+        <v>0.001553891225457198</v>
+      </c>
+      <c r="T35" t="n">
+        <v>7.402240095894243e-05</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0.0007768191773156245</v>
+      </c>
+      <c r="V35" t="n">
+        <v>3.700517750136228e-05</v>
+      </c>
       <c r="W35" t="n">
         <v>7.927083333333333</v>
       </c>
@@ -12335,12 +15375,24 @@
       <c r="AB35" t="n">
         <v>30.597</v>
       </c>
-      <c r="AC35" t="inlineStr"/>
-      <c r="AD35" t="inlineStr"/>
-      <c r="AE35" t="inlineStr"/>
-      <c r="AF35" t="inlineStr"/>
-      <c r="AG35" t="inlineStr"/>
-      <c r="AH35" t="inlineStr"/>
+      <c r="AC35" t="n">
+        <v>0.001580429492605539</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.001356503368364322</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0.001622191286414024</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0.0007900861515515403</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0.0006781413096200486</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0.0008109636504253674</v>
+      </c>
       <c r="AI35" t="n">
         <v>7.7763671875</v>
       </c>
@@ -12360,9 +15412,13 @@
           <t>[{'name': 'void at::native::reduce_kernel&lt;128, 4, at::native::ReduceOp&lt;c10:...', 'stream': 0, 'mean_duration_us': np.float64(7.93)}]</t>
         </is>
       </c>
-      <c r="AN35" t="inlineStr"/>
+      <c r="AN35" t="inlineStr">
+        <is>
+          <t>{'num_input_elems': 6144, 'num_output_elems': 1, 'dtype_in_out': ('c10::BFloat16', None), 'reduce_type': 'mean'}</t>
+        </is>
+      </c>
       <c r="AO35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP35" t="n">
         <v>0.07936813357540853</v>

--- a/tests/traces/mi300/facebook_timesformer-base-finetuned-k400__1016002_perf_report.xlsx
+++ b/tests/traces/mi300/facebook_timesformer-base-finetuned-k400__1016002_perf_report.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="gpu_timeline" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="ops_summary_by_category" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="ops_summary" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="ops_unique_args" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="unified_perf_summary" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="GEMM" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="CONV_fwd" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="BinaryElementwise" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="UnaryElementwise" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Normalization" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Reduce_fwd" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="kernel_summary" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="short_kernel_histogram" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="short_kernels_summary" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gpu_timeline" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ops_summary_by_category" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ops_summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ops_unique_args" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unified_perf_summary" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GEMM" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONV_fwd" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BinaryElementwise" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UnaryElementwise" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Normalization" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reduce_fwd" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="kernel_summary" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="short_kernel_histogram" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="short_kernels_summary" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5127,7 +5127,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>{'elementwise', 'other'}</t>
+          <t>{'other', 'elementwise'}</t>
         </is>
       </c>
       <c r="H6" t="n">

--- a/tests/traces/mi300/facebook_timesformer-base-finetuned-k400__1016002_perf_report.xlsx
+++ b/tests/traces/mi300/facebook_timesformer-base-finetuned-k400__1016002_perf_report.xlsx
@@ -14,8 +14,8 @@
     <sheet name="unified_perf_summary" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="GEMM" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="CONV_fwd" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="BinaryElementwise" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="UnaryElementwise" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="UnaryElementwise" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="BinaryElementwise" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Normalization" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="Reduce_fwd" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="kernel_summary" sheetId="12" state="visible" r:id="rId12"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 0, 'count': 13, 'total_duration_us': np.float64(805.7570000000002), 'mean_duration_us': np.float64(61.98130769230771), 'median_duration_us': np.float64(61.42), 'std_dev_duration_us': np.float64(2.199648936486679), 'min_duration_us': np.float64(59.376), 'max_duration_us': np.float64(65.83)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 0, 'gpu_op_uid': 49078, 'count': 13, 'total_duration_us': np.float64(805.7570000000002), 'mean_duration_us': np.float64(61.98130769230771), 'median_duration_us': np.float64(61.42), 'std_dev_duration_us': np.float64(2.199648936486679), 'min_duration_us': np.float64(59.376), 'max_duration_us': np.float64(65.83)}]</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 0, 'count': 13, 'total_duration_us': np.float64(805.7570000000002), 'mean_duration_us': np.float64(61.98130769230771), 'median_duration_us': np.float64(61.42), 'std_dev_duration_us': np.float64(2.199648936486679), 'min_duration_us': np.float64(59.376), 'max_duration_us': np.float64(65.83)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 0, 'gpu_op_uid': 49078, 'count': 13, 'total_duration_us': np.float64(805.7570000000002), 'mean_duration_us': np.float64(61.98130769230771), 'median_duration_us': np.float64(61.42), 'std_dev_duration_us': np.float64(2.199648936486679), 'min_duration_us': np.float64(59.376), 'max_duration_us': np.float64(65.83)}]</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 0, 'count': 12, 'total_duration_us': np.float64(790.926), 'mean_duration_us': np.float64(65.9105), 'median_duration_us': np.float64(66.7325), 'std_dev_duration_us': np.float64(3.1599893591593005), 'min_duration_us': np.float64(59.015), 'max_duration_us': np.float64(69.599)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 0, 'gpu_op_uid': 49014, 'count': 12, 'total_duration_us': np.float64(790.926), 'mean_duration_us': np.float64(65.9105), 'median_duration_us': np.float64(66.7325), 'std_dev_duration_us': np.float64(3.1599893591593005), 'min_duration_us': np.float64(59.015), 'max_duration_us': np.float64(69.599)}]</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 0, 'count': 12, 'total_duration_us': np.float64(790.926), 'mean_duration_us': np.float64(65.9105), 'median_duration_us': np.float64(66.7325), 'std_dev_duration_us': np.float64(3.1599893591593005), 'min_duration_us': np.float64(59.015), 'max_duration_us': np.float64(69.599)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 0, 'gpu_op_uid': 49014, 'count': 12, 'total_duration_us': np.float64(790.926), 'mean_duration_us': np.float64(65.9105), 'median_duration_us': np.float64(66.7325), 'std_dev_duration_us': np.float64(3.1599893591593005), 'min_duration_us': np.float64(59.015), 'max_duration_us': np.float64(69.599)}]</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 0, 'count': 12, 'total_duration_us': np.float64(703.483), 'mean_duration_us': np.float64(58.62358333333333), 'median_duration_us': np.float64(58.673500000000004), 'std_dev_duration_us': np.float64(2.3749258394854253), 'min_duration_us': np.float64(55.326), 'max_duration_us': np.float64(62.663)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 0, 'gpu_op_uid': 49046, 'count': 12, 'total_duration_us': np.float64(703.483), 'mean_duration_us': np.float64(58.62358333333333), 'median_duration_us': np.float64(58.673500000000004), 'std_dev_duration_us': np.float64(2.3749258394854253), 'min_duration_us': np.float64(55.326), 'max_duration_us': np.float64(62.663)}]</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 0, 'count': 12, 'total_duration_us': np.float64(703.483), 'mean_duration_us': np.float64(58.62358333333333), 'median_duration_us': np.float64(58.673500000000004), 'std_dev_duration_us': np.float64(2.3749258394854253), 'min_duration_us': np.float64(55.326), 'max_duration_us': np.float64(62.663)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 0, 'gpu_op_uid': 49046, 'count': 12, 'total_duration_us': np.float64(703.483), 'mean_duration_us': np.float64(58.62358333333333), 'median_duration_us': np.float64(58.673500000000004), 'std_dev_duration_us': np.float64(2.3749258394854253), 'min_duration_us': np.float64(55.326), 'max_duration_us': np.float64(62.663)}]</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::reduce_kernel&lt;128, 4, at::native::ReduceOp&lt;c10::BFloat16, at::native::MeanOps&lt;c10::BFloat16, float, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::MeanOps&lt;c10::BFloat16, float, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt;)', 'stream': 0, 'count': 12, 'total_duration_us': np.float64(95.12499999999999), 'mean_duration_us': np.float64(7.927083333333332), 'median_duration_us': np.float64(7.7765), 'std_dev_duration_us': np.float64(0.39327184371062673), 'min_duration_us': np.float64(7.576), 'max_duration_us': np.float64(9.06)}]</t>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;128, 4, at::native::ReduceOp&lt;c10::BFloat16, at::native::MeanOps&lt;c10::BFloat16, float, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::MeanOps&lt;c10::BFloat16, float, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt;)', 'stream': 0, 'gpu_op_uid': 49068, 'count': 12, 'total_duration_us': np.float64(95.12499999999999), 'mean_duration_us': np.float64(7.927083333333332), 'median_duration_us': np.float64(7.7765), 'std_dev_duration_us': np.float64(0.39327184371062673), 'min_duration_us': np.float64(7.576), 'max_duration_us': np.float64(9.06)}]</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -9537,7 +9537,7 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::cunn_SoftMaxForwardReg&lt;c10::BFloat16, float, c10::BFloat16, at::native::(anonymous namespace)::SoftMaxForwardEpilogue, long, 4&gt;(c10::BFloat16*, c10::BFloat16 const*, long)', 'stream': 0, 'count': 12, 'total_duration_us': np.float64(41722.677), 'mean_duration_us': np.float64(3476.8897500000003), 'median_duration_us': np.float64(3451.752), 'std_dev_duration_us': np.float64(66.46724565794922), 'min_duration_us': np.float64(3406.829), 'max_duration_us': np.float64(3656.282)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::cunn_SoftMaxForwardReg&lt;c10::BFloat16, float, c10::BFloat16, at::native::(anonymous namespace)::SoftMaxForwardEpilogue, long, 4&gt;(c10::BFloat16*, c10::BFloat16 const*, long)', 'stream': 0, 'gpu_op_uid': 49058, 'count': 12, 'total_duration_us': np.float64(41722.677), 'mean_duration_us': np.float64(3476.8897500000003), 'median_duration_us': np.float64(3451.752), 'std_dev_duration_us': np.float64(66.46724565794922), 'min_duration_us': np.float64(3406.829), 'max_duration_us': np.float64(3656.282)}]</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT128x256x32_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB4_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA1024_LBSPPB256_LBSPPM0_LPA0_LPB4_LPM0_LRVW4_LWPMn1_MIAV0_MIWT8_4_MO40_NTn1_NTA0_NTB0_NTC0_NTD4_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW8_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA8_VWB4_WSGRA0_WSGRB0_WS64_WG16_16_1', 'stream': 0, 'count': 12, 'total_duration_us': np.float64(14545.617999999999), 'mean_duration_us': np.float64(1212.1348333333333), 'median_duration_us': np.float64(1211.283), 'std_dev_duration_us': np.float64(11.187026748525364), 'min_duration_us': np.float64(1191.738), 'max_duration_us': np.float64(1232.471)}]</t>
+          <t>[{'name': 'Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT128x256x32_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB4_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA1024_LBSPPB256_LBSPPM0_LPA0_LPB4_LPM0_LRVW4_LWPMn1_MIAV0_MIWT8_4_MO40_NTn1_NTA0_NTB0_NTC0_NTD4_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW8_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA8_VWB4_WSGRA0_WSGRB0_WS64_WG16_16_1', 'stream': 0, 'gpu_op_uid': 49054, 'count': 12, 'total_duration_us': np.float64(14545.617999999999), 'mean_duration_us': np.float64(1212.1348333333333), 'median_duration_us': np.float64(1211.283), 'std_dev_duration_us': np.float64(11.187026748525364), 'min_duration_us': np.float64(1191.738), 'max_duration_us': np.float64(1232.471)}]</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
@@ -9847,7 +9847,7 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x448x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA2_GRVWB2_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA128_LBSPPB128_LBSPPM0_LPA16_LPB4_LPM0_LRVW4_LWPMn1_MIAV0_MIWT1_7_MO40_NTn1_NTA0_NTB4_NTC0_NTD4_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_16_1', 'stream': 0, 'count': 12, 'total_duration_us': np.float64(13710.097999999998), 'mean_duration_us': np.float64(1142.5081666666665), 'median_duration_us': np.float64(1156.6174999999998), 'std_dev_duration_us': np.float64(84.56194532494443), 'min_duration_us': np.float64(876.333), 'max_duration_us': np.float64(1221.767)}]</t>
+          <t>[{'name': 'Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x448x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA2_GRVWB2_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA128_LBSPPB128_LBSPPM0_LPA16_LPB4_LPM0_LRVW4_LWPMn1_MIAV0_MIWT1_7_MO40_NTn1_NTA0_NTB4_NTC0_NTD4_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_16_1', 'stream': 0, 'gpu_op_uid': 49022, 'count': 12, 'total_duration_us': np.float64(13710.097999999998), 'mean_duration_us': np.float64(1142.5081666666665), 'median_duration_us': np.float64(1156.6174999999998), 'std_dev_duration_us': np.float64(84.56194532494443), 'min_duration_us': np.float64(876.333), 'max_duration_us': np.float64(1221.767)}]</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -10004,7 +10004,7 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 12, 'total_duration_us': np.float64(10958.534), 'mean_duration_us': np.float64(913.2111666666666), 'median_duration_us': np.float64(915.864), 'std_dev_duration_us': np.float64(5.93463524340141), 'min_duration_us': np.float64(898.464), 'max_duration_us': np.float64(919.793)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'gpu_op_uid': 49056, 'count': 12, 'total_duration_us': np.float64(10958.534), 'mean_duration_us': np.float64(913.2111666666666), 'median_duration_us': np.float64(915.864), 'std_dev_duration_us': np.float64(5.93463524340141), 'min_duration_us': np.float64(898.464), 'max_duration_us': np.float64(919.793)}]</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -10161,7 +10161,7 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT64x224x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA1024_LBSPPB128_LBSPPM0_LPA32_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT2_7_MO40_NTn1_NTA0_NTB4_NTC0_NTD4_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW2_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA2_VWB1_WSGRA0_WSGRB0_WS64_WG32_8_1', 'stream': 0, 'count': 12, 'total_duration_us': np.float64(9716.842), 'mean_duration_us': np.float64(809.7368333333334), 'median_duration_us': np.float64(810.0809999999999), 'std_dev_duration_us': np.float64(3.9871760230630486), 'min_duration_us': np.float64(804.769), 'max_duration_us': np.float64(817.117)}]</t>
+          <t>[{'name': 'Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT64x224x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA1024_LBSPPB128_LBSPPM0_LPA32_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT2_7_MO40_NTn1_NTA0_NTB4_NTC0_NTD4_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW2_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA2_VWB1_WSGRA0_WSGRB0_WS64_WG32_8_1', 'stream': 0, 'gpu_op_uid': 49062, 'count': 12, 'total_duration_us': np.float64(9716.842), 'mean_duration_us': np.float64(809.7368333333334), 'median_duration_us': np.float64(810.0809999999999), 'std_dev_duration_us': np.float64(3.9871760230630486), 'min_duration_us': np.float64(804.769), 'max_duration_us': np.float64(817.117)}]</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -10318,7 +10318,7 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x16x32_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB2_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA2048_LBSPPB128_LBSPPM0_LPA0_LPB4_LPM0_LRVW4_LWPMn1_MIAV0_MIWT4_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD4_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW4_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA4_VWB1_WSGRA0_WSGRB0_WS64_WG64_4_1', 'stream': 0, 'count': 12, 'total_duration_us': np.float64(3356.223), 'mean_duration_us': np.float64(279.68525), 'median_duration_us': np.float64(280.7645), 'std_dev_duration_us': np.float64(16.826475344552502), 'min_duration_us': np.float64(246.526), 'max_duration_us': np.float64(310.312)}]</t>
+          <t>[{'name': 'Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x16x32_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB2_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA2048_LBSPPB128_LBSPPM0_LPA0_LPB4_LPM0_LRVW4_LWPMn1_MIAV0_MIWT4_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD4_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW4_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA4_VWB1_WSGRA0_WSGRB0_WS64_WG64_4_1', 'stream': 0, 'gpu_op_uid': 49030, 'count': 12, 'total_duration_us': np.float64(3356.223), 'mean_duration_us': np.float64(279.68525), 'median_duration_us': np.float64(280.7645), 'std_dev_duration_us': np.float64(16.826475344552502), 'min_duration_us': np.float64(246.526), 'max_duration_us': np.float64(310.312)}]</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -10475,7 +10475,7 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x224x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA2_GRVWB2_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA1024_LBSPPB128_LBSPPM0_LPA4_LPB4_LPM0_LRVW4_LWPMn1_MIAV0_MIWT8_7_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW8_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA8_VWB1_WSGRA0_WSGRB0_WS64_WG32_8_1', 'stream': 0, 'count': 12, 'total_duration_us': np.float64(3057.256), 'mean_duration_us': np.float64(254.77133333333333), 'median_duration_us': np.float64(253.0405), 'std_dev_duration_us': np.float64(3.8628236074434144), 'min_duration_us': np.float64(250.615), 'max_duration_us': np.float64(262.162)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x224x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA2_GRVWB2_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA1024_LBSPPB128_LBSPPM0_LPA4_LPB4_LPM0_LRVW4_LWPMn1_MIAV0_MIWT8_7_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW8_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA8_VWB1_WSGRA0_WSGRB0_WS64_WG32_8_1', 'stream': 0, 'gpu_op_uid': 49080, 'count': 12, 'total_duration_us': np.float64(3057.256), 'mean_duration_us': np.float64(254.77133333333333), 'median_duration_us': np.float64(253.0405), 'std_dev_duration_us': np.float64(3.8628236074434144), 'min_duration_us': np.float64(250.615), 'max_duration_us': np.float64(262.162)}]</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -10632,7 +10632,7 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x128x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA1024_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT8_4_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW8_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA8_VWB4_WSGRA0_WSGRB0_WS64_WG32_8_1', 'stream': 0, 'count': 12, 'total_duration_us': np.float64(2600.847), 'mean_duration_us': np.float64(216.73725000000002), 'median_duration_us': np.float64(218.561), 'std_dev_duration_us': np.float64(5.201450440742469), 'min_duration_us': np.float64(205.03), 'max_duration_us': np.float64(222.872)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x128x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA1024_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT8_4_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW8_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA8_VWB4_WSGRA0_WSGRB0_WS64_WG32_8_1', 'stream': 0, 'gpu_op_uid': 49084, 'count': 12, 'total_duration_us': np.float64(2600.847), 'mean_duration_us': np.float64(216.73725000000002), 'median_duration_us': np.float64(218.561), 'std_dev_duration_us': np.float64(5.201450440742469), 'min_duration_us': np.float64(205.03), 'max_duration_us': np.float64(222.872)}]</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -10789,7 +10789,7 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x192x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA1024_LBSPPB256_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT8_6_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW8_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA8_VWB2_WSGRA0_WSGRB0_WS64_WG32_8_1', 'stream': 0, 'count': 12, 'total_duration_us': np.float64(2310.257), 'mean_duration_us': np.float64(192.52141666666668), 'median_duration_us': np.float64(192.98250000000002), 'std_dev_duration_us': np.float64(6.2790327075956185), 'min_duration_us': np.float64(179.051), 'max_duration_us': np.float64(201.462)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x192x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA1024_LBSPPB256_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT8_6_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW8_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA8_VWB2_WSGRA0_WSGRB0_WS64_WG32_8_1', 'stream': 0, 'gpu_op_uid': 49048, 'count': 12, 'total_duration_us': np.float64(2310.257), 'mean_duration_us': np.float64(192.52141666666668), 'median_duration_us': np.float64(192.98250000000002), 'std_dev_duration_us': np.float64(6.2790327075956185), 'min_duration_us': np.float64(179.051), 'max_duration_us': np.float64(201.462)}]</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -10946,7 +10946,7 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x192x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA1024_LBSPPB256_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT8_6_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW8_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA8_VWB2_WSGRA0_WSGRB0_WS64_WG32_8_1', 'stream': 0, 'count': 12, 'total_duration_us': np.float64(2241.0190000000002), 'mean_duration_us': np.float64(186.75158333333334), 'median_duration_us': np.float64(185.906), 'std_dev_duration_us': np.float64(5.873673700764756), 'min_duration_us': np.float64(180.574), 'max_duration_us': np.float64(202.905)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x192x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA1024_LBSPPB256_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT8_6_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW8_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA8_VWB2_WSGRA0_WSGRB0_WS64_WG32_8_1', 'stream': 0, 'gpu_op_uid': 49016, 'count': 12, 'total_duration_us': np.float64(2241.0190000000002), 'mean_duration_us': np.float64(186.75158333333334), 'median_duration_us': np.float64(185.906), 'std_dev_duration_us': np.float64(5.873673700764756), 'min_duration_us': np.float64(180.574), 'max_duration_us': np.float64(202.905)}]</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -11103,7 +11103,7 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 12, 'total_duration_us': np.float64(1910.6989999999998), 'mean_duration_us': np.float64(159.22491666666664), 'median_duration_us': np.float64(159.806), 'std_dev_duration_us': np.float64(4.617114114147013), 'min_duration_us': np.float64(148.54), 'max_duration_us': np.float64(167.624)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'gpu_op_uid': 49052, 'count': 12, 'total_duration_us': np.float64(1910.6989999999998), 'mean_duration_us': np.float64(159.22491666666664), 'median_duration_us': np.float64(159.806), 'std_dev_duration_us': np.float64(4.617114114147013), 'min_duration_us': np.float64(148.54), 'max_duration_us': np.float64(167.624)}]</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -11260,7 +11260,7 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x128x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB1024_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT4_8_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW4_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA4_VWB8_WSGRA0_WSGRB0_WS64_WG64_4_1', 'stream': 0, 'count': 24, 'total_duration_us': np.float64(1705.616), 'mean_duration_us': np.float64(71.06733333333334), 'median_duration_us': np.float64(70.7815), 'std_dev_duration_us': np.float64(2.4860613204200916), 'min_duration_us': np.float64(66.512), 'max_duration_us': np.float64(78.86)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x128x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB1024_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT4_8_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW4_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA4_VWB8_WSGRA0_WSGRB0_WS64_WG64_4_1', 'stream': 0, 'gpu_op_uid': 49034, 'count': 24, 'total_duration_us': np.float64(1705.616), 'mean_duration_us': np.float64(71.06733333333334), 'median_duration_us': np.float64(70.7815), 'std_dev_duration_us': np.float64(2.4860613204200916), 'min_duration_us': np.float64(66.512), 'max_duration_us': np.float64(78.86)}]</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -11387,7 +11387,7 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 12, 'total_duration_us': np.float64(1209.5659999999998), 'mean_duration_us': np.float64(100.79716666666666), 'median_duration_us': np.float64(99.708), 'std_dev_duration_us': np.float64(3.2676696801985496), 'min_duration_us': np.float64(96.38), 'max_duration_us': np.float64(107.646)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'gpu_op_uid': 49082, 'count': 12, 'total_duration_us': np.float64(1209.5659999999998), 'mean_duration_us': np.float64(100.79716666666666), 'median_duration_us': np.float64(99.708), 'std_dev_duration_us': np.float64(3.2676696801985496), 'min_duration_us': np.float64(96.38), 'max_duration_us': np.float64(107.646)}]</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -11532,7 +11532,7 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy HtoD (Host -&gt; Device)', 'stream': 0, 'count': 1, 'total_duration_us': np.float64(1089.783), 'mean_duration_us': np.float64(1089.783), 'median_duration_us': np.float64(1089.783), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(1089.783), 'max_duration_us': np.float64(1089.783)}]</t>
+          <t>[{'name': 'Memcpy HtoD (Host -&gt; Device)', 'stream': 0, 'gpu_op_uid': 48986, 'count': 1, 'total_duration_us': np.float64(1089.783), 'mean_duration_us': np.float64(1089.783), 'median_duration_us': np.float64(1089.783), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(1089.783), 'max_duration_us': np.float64(1089.783)}]</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x128x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB1024_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT4_8_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW4_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA4_VWB8_WSGRA0_WSGRB0_WS64_WG64_4_1', 'stream': 0, 'count': 12, 'total_duration_us': np.float64(890.515), 'mean_duration_us': np.float64(74.20958333333333), 'median_duration_us': np.float64(74.31), 'std_dev_duration_us': np.float64(0.7594008008877068), 'min_duration_us': np.float64(72.646), 'max_duration_us': np.float64(75.212)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x128x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB1024_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT4_8_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW4_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA4_VWB8_WSGRA0_WSGRB0_WS64_WG64_4_1', 'stream': 0, 'gpu_op_uid': 49066, 'count': 12, 'total_duration_us': np.float64(890.515), 'mean_duration_us': np.float64(74.20958333333333), 'median_duration_us': np.float64(74.31), 'std_dev_duration_us': np.float64(0.7594008008877068), 'min_duration_us': np.float64(72.646), 'max_duration_us': np.float64(75.212)}]</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -11846,7 +11846,7 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 0, 'count': 13, 'total_duration_us': np.float64(805.7570000000002), 'mean_duration_us': np.float64(61.98130769230771), 'median_duration_us': np.float64(61.42), 'std_dev_duration_us': np.float64(2.199648936486679), 'min_duration_us': np.float64(59.376), 'max_duration_us': np.float64(65.83)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 0, 'gpu_op_uid': 49078, 'count': 13, 'total_duration_us': np.float64(805.7570000000002), 'mean_duration_us': np.float64(61.98130769230771), 'median_duration_us': np.float64(61.42), 'std_dev_duration_us': np.float64(2.199648936486679), 'min_duration_us': np.float64(59.376), 'max_duration_us': np.float64(65.83)}]</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -12003,7 +12003,7 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 0, 'count': 12, 'total_duration_us': np.float64(790.926), 'mean_duration_us': np.float64(65.9105), 'median_duration_us': np.float64(66.7325), 'std_dev_duration_us': np.float64(3.1599893591593005), 'min_duration_us': np.float64(59.015), 'max_duration_us': np.float64(69.599)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 0, 'gpu_op_uid': 49014, 'count': 12, 'total_duration_us': np.float64(790.926), 'mean_duration_us': np.float64(65.9105), 'median_duration_us': np.float64(66.7325), 'std_dev_duration_us': np.float64(3.1599893591593005), 'min_duration_us': np.float64(59.015), 'max_duration_us': np.float64(69.599)}]</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -12160,7 +12160,7 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 24, 'total_duration_us': np.float64(712.733), 'mean_duration_us': np.float64(29.697208333333332), 'median_duration_us': np.float64(30.0285), 'std_dev_duration_us': np.float64(1.2709403991784545), 'min_duration_us': np.float64(27.101), 'max_duration_us': np.float64(31.832)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'gpu_op_uid': 49018, 'count': 24, 'total_duration_us': np.float64(712.733), 'mean_duration_us': np.float64(29.697208333333332), 'median_duration_us': np.float64(30.0285), 'std_dev_duration_us': np.float64(1.2709403991784545), 'min_duration_us': np.float64(27.101), 'max_duration_us': np.float64(31.832)}]</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -12317,7 +12317,7 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 0, 'count': 12, 'total_duration_us': np.float64(703.483), 'mean_duration_us': np.float64(58.62358333333333), 'median_duration_us': np.float64(58.673500000000004), 'std_dev_duration_us': np.float64(2.3749258394854253), 'min_duration_us': np.float64(55.326), 'max_duration_us': np.float64(62.663)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 0, 'gpu_op_uid': 49046, 'count': 12, 'total_duration_us': np.float64(703.483), 'mean_duration_us': np.float64(58.62358333333333), 'median_duration_us': np.float64(58.673500000000004), 'std_dev_duration_us': np.float64(2.3749258394854253), 'min_duration_us': np.float64(55.326), 'max_duration_us': np.float64(62.663)}]</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 24, 'total_duration_us': np.float64(689.8420000000001), 'mean_duration_us': np.float64(28.743416666666672), 'median_duration_us': np.float64(29.4665), 'std_dev_duration_us': np.float64(1.3861626563005591), 'min_duration_us': np.float64(26.66), 'max_duration_us': np.float64(30.629)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'gpu_op_uid': 49050, 'count': 24, 'total_duration_us': np.float64(689.8420000000001), 'mean_duration_us': np.float64(28.743416666666672), 'median_duration_us': np.float64(29.4665), 'std_dev_duration_us': np.float64(1.3861626563005591), 'min_duration_us': np.float64(26.66), 'max_duration_us': np.float64(30.629)}]</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
@@ -12631,7 +12631,7 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 24, 'total_duration_us': np.float64(684.548), 'mean_duration_us': np.float64(28.522833333333335), 'median_duration_us': np.float64(28.2845), 'std_dev_duration_us': np.float64(1.7633981320797134), 'min_duration_us': np.float64(25.898), 'max_duration_us': np.float64(32.995)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'gpu_op_uid': 49076, 'count': 24, 'total_duration_us': np.float64(684.548), 'mean_duration_us': np.float64(28.522833333333335), 'median_duration_us': np.float64(28.2845), 'std_dev_duration_us': np.float64(1.7633981320797134), 'min_duration_us': np.float64(25.898), 'max_duration_us': np.float64(32.995)}]</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
@@ -12758,7 +12758,7 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 3, 64, 64&gt;(at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;*, at::native::(anonymous namespace)::CatArrInputTensorMetadata&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 64, 64&gt;, at::native::(anonymous namespace)::TensorSizeStride&lt;unsigned int, 4u&gt;, int, unsigned int)', 'stream': 0, 'count': 12, 'total_duration_us': np.float64(551.897), 'mean_duration_us': np.float64(45.99141666666667), 'median_duration_us': np.float64(45.3635), 'std_dev_duration_us': np.float64(1.8339345434671928), 'min_duration_us': np.float64(44.02), 'max_duration_us': np.float64(49.553)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 3, 64, 64&gt;(at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;*, at::native::(anonymous namespace)::CatArrInputTensorMetadata&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 64, 64&gt;, at::native::(anonymous namespace)::TensorSizeStride&lt;unsigned int, 4u&gt;, int, unsigned int)', 'stream': 0, 'gpu_op_uid': 49044, 'count': 12, 'total_duration_us': np.float64(551.897), 'mean_duration_us': np.float64(45.99141666666667), 'median_duration_us': np.float64(45.3635), 'std_dev_duration_us': np.float64(1.8339345434671928), 'min_duration_us': np.float64(44.02), 'max_duration_us': np.float64(49.553)}]</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
@@ -12911,7 +12911,7 @@
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 12, 'total_duration_us': np.float64(484.30300000000005), 'mean_duration_us': np.float64(40.358583333333335), 'median_duration_us': np.float64(41.013999999999996), 'std_dev_duration_us': np.float64(2.2839961127496595), 'min_duration_us': np.float64(33.116), 'max_duration_us': np.float64(42.456)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'gpu_op_uid': 49020, 'count': 12, 'total_duration_us': np.float64(484.30300000000005), 'mean_duration_us': np.float64(40.358583333333335), 'median_duration_us': np.float64(41.013999999999996), 'std_dev_duration_us': np.float64(2.2839961127496595), 'min_duration_us': np.float64(33.116), 'max_duration_us': np.float64(42.456)}]</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
@@ -13038,7 +13038,7 @@
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::CatArrayBatchedCopy_contig&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 3, 128, 1&gt;(at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;*, at::native::(anonymous namespace)::CatArrInputTensorMetadata&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 128, 1&gt;, at::native::(anonymous namespace)::TensorSizeStride&lt;unsigned int, 4u&gt;, int, unsigned int)', 'stream': 0, 'count': 12, 'total_duration_us': np.float64(459.0420000000001), 'mean_duration_us': np.float64(38.25350000000001), 'median_duration_us': np.float64(38.167), 'std_dev_duration_us': np.float64(0.9562089642611244), 'min_duration_us': np.float64(37.084), 'max_duration_us': np.float64(39.65)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::CatArrayBatchedCopy_contig&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 3, 128, 1&gt;(at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;*, at::native::(anonymous namespace)::CatArrInputTensorMetadata&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 128, 1&gt;, at::native::(anonymous namespace)::TensorSizeStride&lt;unsigned int, 4u&gt;, int, unsigned int)', 'stream': 0, 'gpu_op_uid': 49072, 'count': 12, 'total_duration_us': np.float64(459.0420000000001), 'mean_duration_us': np.float64(38.25350000000001), 'median_duration_us': np.float64(38.167), 'std_dev_duration_us': np.float64(0.9562089642611244), 'min_duration_us': np.float64(37.084), 'max_duration_us': np.float64(39.65)}]</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
@@ -13191,7 +13191,7 @@
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 12, 'total_duration_us': np.float64(432.103), 'mean_duration_us': np.float64(36.008583333333334), 'median_duration_us': np.float64(35.941500000000005), 'std_dev_duration_us': np.float64(0.6513263977368714), 'min_duration_us': np.float64(35.24), 'max_duration_us': np.float64(37.606)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'gpu_op_uid': 49070, 'count': 12, 'total_duration_us': np.float64(432.103), 'mean_duration_us': np.float64(36.008583333333334), 'median_duration_us': np.float64(35.941500000000005), 'std_dev_duration_us': np.float64(0.6513263977368714), 'min_duration_us': np.float64(35.24), 'max_duration_us': np.float64(37.606)}]</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
@@ -13340,7 +13340,7 @@
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>[{'name': 'SubTensorOpWithScalar1d', 'stream': 0, 'count': 1, 'total_duration_us': np.float64(16.396), 'mean_duration_us': np.float64(16.396), 'median_duration_us': np.float64(16.396), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(16.396), 'max_duration_us': np.float64(16.396)}, {'name': 'batched_transpose_256x4_half', 'stream': 0, 'count': 1, 'total_duration_us': np.float64(33.917), 'mean_duration_us': np.float64(33.917), 'median_duration_us': np.float64(33.917), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(33.917), 'max_duration_us': np.float64(33.917)}, {'name': 'batched_transpose_128x4_half', 'stream': 0, 'count': 1, 'total_duration_us': np.float64(4.891), 'mean_duration_us': np.float64(4.891), 'median_duration_us': np.float64(4.891), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(4.891), 'max_duration_us': np.float64(4.891)}, {'name': 'igemm_fwd_gtcx3_nhwc_bf16_bx0_ex1_bt256x64x8_wt64x16x4_ws1x1_wr2x2_ta1x1x8x1_1x8x1x32_tb1x1x2x1_1x8x1x32_me', 'stream': 0, 'count': 1, 'total_duration_us': np.float64(246.806), 'mean_duration_us': np.float64(246.806), 'median_duration_us': np.float64(246.806), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(246.806), 'max_duration_us': np.float64(246.806)}, {'name': 'batched_transpose_32x16_half', 'stream': 0, 'count': 1, 'total_duration_us': np.float64(32.032), 'mean_duration_us': np.float64(32.032), 'median_duration_us': np.float64(32.032), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(32.032), 'max_duration_us': np.float64(32.032)}, {'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 1, 'total_duration_us': np.float64(51.999), 'mean_duration_us': np.float64(51.999), 'median_duration_us': np.float64(51.999), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(51.999), 'max_duration_us': np.float64(51.999)}]</t>
+          <t>[{'name': 'SubTensorOpWithScalar1d', 'stream': 0, 'gpu_op_uid': 48988, 'count': 1, 'total_duration_us': np.float64(16.396), 'mean_duration_us': np.float64(16.396), 'median_duration_us': np.float64(16.396), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(16.396), 'max_duration_us': np.float64(16.396)}, {'name': 'batched_transpose_256x4_half', 'stream': 0, 'gpu_op_uid': 48990, 'count': 1, 'total_duration_us': np.float64(33.917), 'mean_duration_us': np.float64(33.917), 'median_duration_us': np.float64(33.917), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(33.917), 'max_duration_us': np.float64(33.917)}, {'name': 'batched_transpose_128x4_half', 'stream': 0, 'gpu_op_uid': 48992, 'count': 1, 'total_duration_us': np.float64(4.891), 'mean_duration_us': np.float64(4.891), 'median_duration_us': np.float64(4.891), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(4.891), 'max_duration_us': np.float64(4.891)}, {'name': 'igemm_fwd_gtcx3_nhwc_bf16_bx0_ex1_bt256x64x8_wt64x16x4_ws1x1_wr2x2_ta1x1x8x1_1x8x1x32_tb1x1x2x1_1x8x1x32_me', 'stream': 0, 'gpu_op_uid': 48994, 'count': 1, 'total_duration_us': np.float64(246.806), 'mean_duration_us': np.float64(246.806), 'median_duration_us': np.float64(246.806), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(246.806), 'max_duration_us': np.float64(246.806)}, {'name': 'batched_transpose_32x16_half', 'stream': 0, 'gpu_op_uid': 48996, 'count': 1, 'total_duration_us': np.float64(32.032), 'mean_duration_us': np.float64(32.032), 'median_duration_us': np.float64(32.032), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(32.032), 'max_duration_us': np.float64(32.032)}, {'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'gpu_op_uid': 48998, 'count': 1, 'total_duration_us': np.float64(51.999), 'mean_duration_us': np.float64(51.999), 'median_duration_us': np.float64(51.999), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(51.999), 'max_duration_us': np.float64(51.999)}]</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
@@ -13467,7 +13467,7 @@
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::CatArrayBatchedCopy_contig&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 3, 128, 1&gt;(at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;*, at::native::(anonymous namespace)::CatArrInputTensorMetadata&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 128, 1&gt;, at::native::(anonymous namespace)::TensorSizeStride&lt;unsigned int, 4u&gt;, int, unsigned int)', 'stream': 0, 'count': 12, 'total_duration_us': np.float64(386.03600000000006), 'mean_duration_us': np.float64(32.16966666666667), 'median_duration_us': np.float64(32.132999999999996), 'std_dev_duration_us': np.float64(0.7500032592521766), 'min_duration_us': np.float64(30.91), 'max_duration_us': np.float64(34.117)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::CatArrayBatchedCopy_contig&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 3, 128, 1&gt;(at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;*, at::native::(anonymous namespace)::CatArrInputTensorMetadata&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 128, 1&gt;, at::native::(anonymous namespace)::TensorSizeStride&lt;unsigned int, 4u&gt;, int, unsigned int)', 'stream': 0, 'gpu_op_uid': 49074, 'count': 12, 'total_duration_us': np.float64(386.03600000000006), 'mean_duration_us': np.float64(32.16966666666667), 'median_duration_us': np.float64(32.132999999999996), 'std_dev_duration_us': np.float64(0.7500032592521766), 'min_duration_us': np.float64(30.91), 'max_duration_us': np.float64(34.117)}]</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
@@ -13620,7 +13620,7 @@
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 12, 'total_duration_us': np.float64(360.25499999999994), 'mean_duration_us': np.float64(30.021249999999995), 'median_duration_us': np.float64(30.028), 'std_dev_duration_us': np.float64(0.29395269602437757), 'min_duration_us': np.float64(29.467), 'max_duration_us': np.float64(30.469)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'gpu_op_uid': 49064, 'count': 12, 'total_duration_us': np.float64(360.25499999999994), 'mean_duration_us': np.float64(30.021249999999995), 'median_duration_us': np.float64(30.028), 'std_dev_duration_us': np.float64(0.29395269602437757), 'min_duration_us': np.float64(29.467), 'max_duration_us': np.float64(30.469)}]</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
@@ -13777,7 +13777,7 @@
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 12, 'total_duration_us': np.float64(359.694), 'mean_duration_us': np.float64(29.974500000000003), 'median_duration_us': np.float64(29.487000000000002), 'std_dev_duration_us': np.float64(1.353853789496241), 'min_duration_us': np.float64(29.025), 'max_duration_us': np.float64(34.077)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'gpu_op_uid': 49032, 'count': 12, 'total_duration_us': np.float64(359.694), 'mean_duration_us': np.float64(29.974500000000003), 'median_duration_us': np.float64(29.487000000000002), 'std_dev_duration_us': np.float64(1.353853789496241), 'min_duration_us': np.float64(29.025), 'max_duration_us': np.float64(34.077)}]</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
@@ -13934,7 +13934,7 @@
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 12, 'total_duration_us': np.float64(329.064), 'mean_duration_us': np.float64(27.422), 'median_duration_us': np.float64(27.1415), 'std_dev_duration_us': np.float64(1.5525699125428567), 'min_duration_us': np.float64(24.976), 'max_duration_us': np.float64(30.67)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'gpu_op_uid': 49038, 'count': 12, 'total_duration_us': np.float64(329.064), 'mean_duration_us': np.float64(27.422), 'median_duration_us': np.float64(27.1415), 'std_dev_duration_us': np.float64(1.5525699125428567), 'min_duration_us': np.float64(24.976), 'max_duration_us': np.float64(30.67)}]</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
@@ -14061,7 +14061,7 @@
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>[{'name': 'void (anonymous namespace)::softmax_warp_forward&lt;c10::BFloat16, c10::BFloat16, float, 3, false, false&gt;(c10::BFloat16*, c10::BFloat16 const*, int, int, int, bool const*, int, bool)', 'stream': 0, 'count': 12, 'total_duration_us': np.float64(133.97400000000002), 'mean_duration_us': np.float64(11.164500000000002), 'median_duration_us': np.float64(11.285), 'std_dev_duration_us': np.float64(0.7139774156092054), 'min_duration_us': np.float64(9.34), 'max_duration_us': np.float64(12.227)}]</t>
+          <t>[{'name': 'void (anonymous namespace)::softmax_warp_forward&lt;c10::BFloat16, c10::BFloat16, float, 3, false, false&gt;(c10::BFloat16*, c10::BFloat16 const*, int, int, int, bool const*, int, bool)', 'stream': 0, 'gpu_op_uid': 49026, 'count': 12, 'total_duration_us': np.float64(133.97400000000002), 'mean_duration_us': np.float64(11.164500000000002), 'median_duration_us': np.float64(11.285), 'std_dev_duration_us': np.float64(0.7139774156092054), 'min_duration_us': np.float64(9.34), 'max_duration_us': np.float64(12.227)}]</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
@@ -14206,7 +14206,7 @@
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 1, 'total_duration_us': np.float64(121.759), 'mean_duration_us': np.float64(121.759), 'median_duration_us': np.float64(121.759), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(121.759), 'max_duration_us': np.float64(121.759)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'gpu_op_uid': 49008, 'count': 1, 'total_duration_us': np.float64(121.759), 'mean_duration_us': np.float64(121.759), 'median_duration_us': np.float64(121.759), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(121.759), 'max_duration_us': np.float64(121.759)}]</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
@@ -14329,7 +14329,7 @@
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 3, 64, 64&gt;(at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;*, at::native::(anonymous namespace)::CatArrInputTensorMetadata&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 64, 64&gt;, at::native::(anonymous namespace)::TensorSizeStride&lt;unsigned int, 4u&gt;, int, unsigned int)', 'stream': 0, 'count': 1, 'total_duration_us': np.float64(101.111), 'mean_duration_us': np.float64(101.111), 'median_duration_us': np.float64(101.111), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(101.111), 'max_duration_us': np.float64(101.111)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 3, 64, 64&gt;(at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;*, at::native::(anonymous namespace)::CatArrInputTensorMetadata&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 64, 64&gt;, at::native::(anonymous namespace)::TensorSizeStride&lt;unsigned int, 4u&gt;, int, unsigned int)', 'stream': 0, 'gpu_op_uid': 49000, 'count': 1, 'total_duration_us': np.float64(101.111), 'mean_duration_us': np.float64(101.111), 'median_duration_us': np.float64(101.111), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(101.111), 'max_duration_us': np.float64(101.111)}]</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
@@ -14482,7 +14482,7 @@
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::reduce_kernel&lt;128, 4, at::native::ReduceOp&lt;c10::BFloat16, at::native::MeanOps&lt;c10::BFloat16, float, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::MeanOps&lt;c10::BFloat16, float, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt;)', 'stream': 0, 'count': 12, 'total_duration_us': np.float64(95.12499999999999), 'mean_duration_us': np.float64(7.927083333333332), 'median_duration_us': np.float64(7.7765), 'std_dev_duration_us': np.float64(0.39327184371062673), 'min_duration_us': np.float64(7.576), 'max_duration_us': np.float64(9.06)}]</t>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;128, 4, at::native::ReduceOp&lt;c10::BFloat16, at::native::MeanOps&lt;c10::BFloat16, float, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::MeanOps&lt;c10::BFloat16, float, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt;)', 'stream': 0, 'gpu_op_uid': 49068, 'count': 12, 'total_duration_us': np.float64(95.12499999999999), 'mean_duration_us': np.float64(7.927083333333332), 'median_duration_us': np.float64(7.7765), 'std_dev_duration_us': np.float64(0.39327184371062673), 'min_duration_us': np.float64(7.576), 'max_duration_us': np.float64(9.06)}]</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
@@ -14639,7 +14639,7 @@
       </c>
       <c r="AL36" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 12, 'total_duration_us': np.float64(65.258), 'mean_duration_us': np.float64(5.438166666666667), 'median_duration_us': np.float64(5.5120000000000005), 'std_dev_duration_us': np.float64(0.21539724283802278), 'min_duration_us': np.float64(5.011), 'max_duration_us': np.float64(5.733)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'gpu_op_uid': 49024, 'count': 12, 'total_duration_us': np.float64(65.258), 'mean_duration_us': np.float64(5.438166666666667), 'median_duration_us': np.float64(5.5120000000000005), 'std_dev_duration_us': np.float64(0.21539724283802278), 'min_duration_us': np.float64(5.011), 'max_duration_us': np.float64(5.733)}]</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
@@ -14796,7 +14796,7 @@
       </c>
       <c r="AL37" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 12, 'total_duration_us': np.float64(59.084), 'mean_duration_us': np.float64(4.923666666666667), 'median_duration_us': np.float64(4.9704999999999995), 'std_dev_duration_us': np.float64(0.2903455795350698), 'min_duration_us': np.float64(4.289), 'max_duration_us': np.float64(5.412)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'gpu_op_uid': 49042, 'count': 12, 'total_duration_us': np.float64(59.084), 'mean_duration_us': np.float64(4.923666666666667), 'median_duration_us': np.float64(4.9704999999999995), 'std_dev_duration_us': np.float64(0.2903455795350698), 'min_duration_us': np.float64(4.289), 'max_duration_us': np.float64(5.412)}]</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
@@ -14945,7 +14945,7 @@
       </c>
       <c r="AL38" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 1, 'total_duration_us': np.float64(30.99), 'mean_duration_us': np.float64(30.99), 'median_duration_us': np.float64(30.99), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(30.99), 'max_duration_us': np.float64(30.99)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'gpu_op_uid': 49010, 'count': 1, 'total_duration_us': np.float64(30.99), 'mean_duration_us': np.float64(30.99), 'median_duration_us': np.float64(30.99), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(30.99), 'max_duration_us': np.float64(30.99)}]</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
@@ -15068,7 +15068,7 @@
       </c>
       <c r="AL39" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::CatArrayBatchedCopy_contig&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 3, 128, 1&gt;(at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;*, at::native::(anonymous namespace)::CatArrInputTensorMetadata&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 128, 1&gt;, at::native::(anonymous namespace)::TensorSizeStride&lt;unsigned int, 4u&gt;, int, unsigned int)', 'stream': 0, 'count': 1, 'total_duration_us': np.float64(30.349), 'mean_duration_us': np.float64(30.349), 'median_duration_us': np.float64(30.349), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(30.349), 'max_duration_us': np.float64(30.349)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::CatArrayBatchedCopy_contig&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 3, 128, 1&gt;(at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;*, at::native::(anonymous namespace)::CatArrInputTensorMetadata&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 128, 1&gt;, at::native::(anonymous namespace)::TensorSizeStride&lt;unsigned int, 4u&gt;, int, unsigned int)', 'stream': 0, 'gpu_op_uid': 49012, 'count': 1, 'total_duration_us': np.float64(30.349), 'mean_duration_us': np.float64(30.349), 'median_duration_us': np.float64(30.349), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(30.349), 'max_duration_us': np.float64(30.349)}]</t>
         </is>
       </c>
       <c r="AM39" t="inlineStr">
@@ -15213,7 +15213,7 @@
       </c>
       <c r="AL40" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 1, 'total_duration_us': np.float64(29.788), 'mean_duration_us': np.float64(29.788), 'median_duration_us': np.float64(29.788), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(29.788), 'max_duration_us': np.float64(29.788)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'gpu_op_uid': 49002, 'count': 1, 'total_duration_us': np.float64(29.788), 'mean_duration_us': np.float64(29.788), 'median_duration_us': np.float64(29.788), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(29.788), 'max_duration_us': np.float64(29.788)}]</t>
         </is>
       </c>
       <c r="AM40" t="inlineStr">
@@ -15336,7 +15336,7 @@
       </c>
       <c r="AL41" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 1, 'total_duration_us': np.float64(6.494), 'mean_duration_us': np.float64(6.494), 'median_duration_us': np.float64(6.494), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(6.494), 'max_duration_us': np.float64(6.494)}, {'name': 'void at::native::(anonymous namespace)::upsample_nearest1d_out_frame&lt;c10::BFloat16, &amp;at::native::nearest_neighbor_compute_source_index&gt;(c10::BFloat16 const*, unsigned long, unsigned long, unsigned long, unsigned long, c10::BFloat16*, float)', 'stream': 0, 'count': 1, 'total_duration_us': np.float64(4.208), 'mean_duration_us': np.float64(4.208), 'median_duration_us': np.float64(4.208), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(4.208), 'max_duration_us': np.float64(4.208)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'gpu_op_uid': 49004, 'count': 1, 'total_duration_us': np.float64(6.494), 'mean_duration_us': np.float64(6.494), 'median_duration_us': np.float64(6.494), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(6.494), 'max_duration_us': np.float64(6.494)}, {'name': 'void at::native::(anonymous namespace)::upsample_nearest1d_out_frame&lt;c10::BFloat16, &amp;at::native::nearest_neighbor_compute_source_index&gt;(c10::BFloat16 const*, unsigned long, unsigned long, unsigned long, unsigned long, c10::BFloat16*, float)', 'stream': 0, 'gpu_op_uid': 49006, 'count': 1, 'total_duration_us': np.float64(4.208), 'mean_duration_us': np.float64(4.208), 'median_duration_us': np.float64(4.208), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(4.208), 'max_duration_us': np.float64(4.208)}]</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
@@ -15481,7 +15481,7 @@
       </c>
       <c r="AL42" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMBSK_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD0_NTM0_NEPBS0_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4', 'stream': 0, 'count': 1, 'total_duration_us': np.float64(9.261), 'mean_duration_us': np.float64(9.261), 'median_duration_us': np.float64(9.261), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(9.261), 'max_duration_us': np.float64(9.261)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMBSK_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD0_NTM0_NEPBS0_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4', 'stream': 0, 'gpu_op_uid': 49882, 'count': 1, 'total_duration_us': np.float64(9.261), 'mean_duration_us': np.float64(9.261), 'median_duration_us': np.float64(9.261), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(9.261), 'max_duration_us': np.float64(9.261)}]</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
@@ -15630,7 +15630,7 @@
       </c>
       <c r="AL43" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'count': 1, 'total_duration_us': np.float64(4.208), 'mean_duration_us': np.float64(4.208), 'median_duration_us': np.float64(4.208), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(4.208), 'max_duration_us': np.float64(4.208)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'gpu_op_uid': 49884, 'count': 1, 'total_duration_us': np.float64(4.208), 'mean_duration_us': np.float64(4.208), 'median_duration_us': np.float64(4.208), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(4.208), 'max_duration_us': np.float64(4.208)}]</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
@@ -15986,7 +15986,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT128x256x32_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB4_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA1024_LBSPPB256_LBSPPM0_LPA0_LPB4_LPM0_LRVW4_LWPMn1_MIAV0_MIWT8_4_MO40_NTn1_NTA0_NTB0_NTC0_NTD4_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW8_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA8_VWB4_WSGRA0_WSGRB0_WS64_WG16_16_1', 'stream': 0, 'count': 12, 'total_duration_us': np.float64(14545.617999999999), 'mean_duration_us': np.float64(1212.1348333333333), 'median_duration_us': np.float64(1211.283), 'std_dev_duration_us': np.float64(11.187026748525364), 'min_duration_us': np.float64(1191.738), 'max_duration_us': np.float64(1232.471)}]</t>
+          <t>[{'name': 'Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT128x256x32_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB4_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA1024_LBSPPB256_LBSPPM0_LPA0_LPB4_LPM0_LRVW4_LWPMn1_MIAV0_MIWT8_4_MO40_NTn1_NTA0_NTB0_NTC0_NTD4_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW8_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA8_VWB4_WSGRA0_WSGRB0_WS64_WG16_16_1', 'stream': 0, 'gpu_op_uid': 49054, 'count': 12, 'total_duration_us': np.float64(14545.617999999999), 'mean_duration_us': np.float64(1212.1348333333333), 'median_duration_us': np.float64(1211.283), 'std_dev_duration_us': np.float64(11.187026748525364), 'min_duration_us': np.float64(1191.738), 'max_duration_us': np.float64(1232.471)}]</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -16151,7 +16151,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x448x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA2_GRVWB2_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA128_LBSPPB128_LBSPPM0_LPA16_LPB4_LPM0_LRVW4_LWPMn1_MIAV0_MIWT1_7_MO40_NTn1_NTA0_NTB4_NTC0_NTD4_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_16_1', 'stream': 0, 'count': 12, 'total_duration_us': np.float64(13710.097999999998), 'mean_duration_us': np.float64(1142.5081666666665), 'median_duration_us': np.float64(1156.6174999999998), 'std_dev_duration_us': np.float64(84.56194532494443), 'min_duration_us': np.float64(876.333), 'max_duration_us': np.float64(1221.767)}]</t>
+          <t>[{'name': 'Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x448x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA2_GRVWB2_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA128_LBSPPB128_LBSPPM0_LPA16_LPB4_LPM0_LRVW4_LWPMn1_MIAV0_MIWT1_7_MO40_NTn1_NTA0_NTB4_NTC0_NTD4_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_16_1', 'stream': 0, 'gpu_op_uid': 49022, 'count': 12, 'total_duration_us': np.float64(13710.097999999998), 'mean_duration_us': np.float64(1142.5081666666665), 'median_duration_us': np.float64(1156.6174999999998), 'std_dev_duration_us': np.float64(84.56194532494443), 'min_duration_us': np.float64(876.333), 'max_duration_us': np.float64(1221.767)}]</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT64x224x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA1024_LBSPPB128_LBSPPM0_LPA32_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT2_7_MO40_NTn1_NTA0_NTB4_NTC0_NTD4_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW2_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA2_VWB1_WSGRA0_WSGRB0_WS64_WG32_8_1', 'stream': 0, 'count': 12, 'total_duration_us': np.float64(9716.842), 'mean_duration_us': np.float64(809.7368333333334), 'median_duration_us': np.float64(810.0809999999999), 'std_dev_duration_us': np.float64(3.9871760230630486), 'min_duration_us': np.float64(804.769), 'max_duration_us': np.float64(817.117)}]</t>
+          <t>[{'name': 'Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT64x224x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA1024_LBSPPB128_LBSPPM0_LPA32_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT2_7_MO40_NTn1_NTA0_NTB4_NTC0_NTD4_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW2_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA2_VWB1_WSGRA0_WSGRB0_WS64_WG32_8_1', 'stream': 0, 'gpu_op_uid': 49062, 'count': 12, 'total_duration_us': np.float64(9716.842), 'mean_duration_us': np.float64(809.7368333333334), 'median_duration_us': np.float64(810.0809999999999), 'std_dev_duration_us': np.float64(3.9871760230630486), 'min_duration_us': np.float64(804.769), 'max_duration_us': np.float64(817.117)}]</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -16481,7 +16481,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x16x32_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB2_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA2048_LBSPPB128_LBSPPM0_LPA0_LPB4_LPM0_LRVW4_LWPMn1_MIAV0_MIWT4_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD4_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW4_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA4_VWB1_WSGRA0_WSGRB0_WS64_WG64_4_1', 'stream': 0, 'count': 12, 'total_duration_us': np.float64(3356.223), 'mean_duration_us': np.float64(279.68525), 'median_duration_us': np.float64(280.7645), 'std_dev_duration_us': np.float64(16.826475344552502), 'min_duration_us': np.float64(246.526), 'max_duration_us': np.float64(310.312)}]</t>
+          <t>[{'name': 'Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x16x32_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB2_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA2048_LBSPPB128_LBSPPM0_LPA0_LPB4_LPM0_LRVW4_LWPMn1_MIAV0_MIWT4_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD4_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW4_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA4_VWB1_WSGRA0_WSGRB0_WS64_WG64_4_1', 'stream': 0, 'gpu_op_uid': 49030, 'count': 12, 'total_duration_us': np.float64(3356.223), 'mean_duration_us': np.float64(279.68525), 'median_duration_us': np.float64(280.7645), 'std_dev_duration_us': np.float64(16.826475344552502), 'min_duration_us': np.float64(246.526), 'max_duration_us': np.float64(310.312)}]</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -16646,7 +16646,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x224x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA2_GRVWB2_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA1024_LBSPPB128_LBSPPM0_LPA4_LPB4_LPM0_LRVW4_LWPMn1_MIAV0_MIWT8_7_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW8_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA8_VWB1_WSGRA0_WSGRB0_WS64_WG32_8_1', 'stream': 0, 'count': 12, 'total_duration_us': np.float64(3057.256), 'mean_duration_us': np.float64(254.77133333333333), 'median_duration_us': np.float64(253.0405), 'std_dev_duration_us': np.float64(3.8628236074434144), 'min_duration_us': np.float64(250.615), 'max_duration_us': np.float64(262.162)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x224x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA2_GRVWB2_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA1024_LBSPPB128_LBSPPM0_LPA4_LPB4_LPM0_LRVW4_LWPMn1_MIAV0_MIWT8_7_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW8_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA8_VWB1_WSGRA0_WSGRB0_WS64_WG32_8_1', 'stream': 0, 'gpu_op_uid': 49080, 'count': 12, 'total_duration_us': np.float64(3057.256), 'mean_duration_us': np.float64(254.77133333333333), 'median_duration_us': np.float64(253.0405), 'std_dev_duration_us': np.float64(3.8628236074434144), 'min_duration_us': np.float64(250.615), 'max_duration_us': np.float64(262.162)}]</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -16811,7 +16811,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x128x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA1024_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT8_4_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW8_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA8_VWB4_WSGRA0_WSGRB0_WS64_WG32_8_1', 'stream': 0, 'count': 12, 'total_duration_us': np.float64(2600.847), 'mean_duration_us': np.float64(216.73725000000002), 'median_duration_us': np.float64(218.561), 'std_dev_duration_us': np.float64(5.201450440742469), 'min_duration_us': np.float64(205.03), 'max_duration_us': np.float64(222.872)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x128x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA1024_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT8_4_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW8_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA8_VWB4_WSGRA0_WSGRB0_WS64_WG32_8_1', 'stream': 0, 'gpu_op_uid': 49084, 'count': 12, 'total_duration_us': np.float64(2600.847), 'mean_duration_us': np.float64(216.73725000000002), 'median_duration_us': np.float64(218.561), 'std_dev_duration_us': np.float64(5.201450440742469), 'min_duration_us': np.float64(205.03), 'max_duration_us': np.float64(222.872)}]</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -16976,7 +16976,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x192x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA1024_LBSPPB256_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT8_6_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW8_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA8_VWB2_WSGRA0_WSGRB0_WS64_WG32_8_1', 'stream': 0, 'count': 12, 'total_duration_us': np.float64(2310.257), 'mean_duration_us': np.float64(192.52141666666668), 'median_duration_us': np.float64(192.98250000000002), 'std_dev_duration_us': np.float64(6.2790327075956185), 'min_duration_us': np.float64(179.051), 'max_duration_us': np.float64(201.462)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x192x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA1024_LBSPPB256_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT8_6_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW8_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA8_VWB2_WSGRA0_WSGRB0_WS64_WG32_8_1', 'stream': 0, 'gpu_op_uid': 49048, 'count': 12, 'total_duration_us': np.float64(2310.257), 'mean_duration_us': np.float64(192.52141666666668), 'median_duration_us': np.float64(192.98250000000002), 'std_dev_duration_us': np.float64(6.2790327075956185), 'min_duration_us': np.float64(179.051), 'max_duration_us': np.float64(201.462)}]</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -17141,7 +17141,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x192x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA1024_LBSPPB256_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT8_6_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW8_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA8_VWB2_WSGRA0_WSGRB0_WS64_WG32_8_1', 'stream': 0, 'count': 12, 'total_duration_us': np.float64(2241.0190000000002), 'mean_duration_us': np.float64(186.75158333333334), 'median_duration_us': np.float64(185.906), 'std_dev_duration_us': np.float64(5.873673700764756), 'min_duration_us': np.float64(180.574), 'max_duration_us': np.float64(202.905)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x192x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA1024_LBSPPB256_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT8_6_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW8_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA8_VWB2_WSGRA0_WSGRB0_WS64_WG32_8_1', 'stream': 0, 'gpu_op_uid': 49016, 'count': 12, 'total_duration_us': np.float64(2241.0190000000002), 'mean_duration_us': np.float64(186.75158333333334), 'median_duration_us': np.float64(185.906), 'std_dev_duration_us': np.float64(5.873673700764756), 'min_duration_us': np.float64(180.574), 'max_duration_us': np.float64(202.905)}]</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -17306,7 +17306,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x128x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB1024_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT4_8_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW4_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA4_VWB8_WSGRA0_WSGRB0_WS64_WG64_4_1', 'stream': 0, 'count': 24, 'total_duration_us': np.float64(1705.616), 'mean_duration_us': np.float64(71.06733333333334), 'median_duration_us': np.float64(70.7815), 'std_dev_duration_us': np.float64(2.4860613204200916), 'min_duration_us': np.float64(66.512), 'max_duration_us': np.float64(78.86)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x128x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB1024_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT4_8_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW4_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA4_VWB8_WSGRA0_WSGRB0_WS64_WG64_4_1', 'stream': 0, 'gpu_op_uid': 49034, 'count': 24, 'total_duration_us': np.float64(1705.616), 'mean_duration_us': np.float64(71.06733333333334), 'median_duration_us': np.float64(70.7815), 'std_dev_duration_us': np.float64(2.4860613204200916), 'min_duration_us': np.float64(66.512), 'max_duration_us': np.float64(78.86)}]</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -17471,7 +17471,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x128x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB1024_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT4_8_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW4_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA4_VWB8_WSGRA0_WSGRB0_WS64_WG64_4_1', 'stream': 0, 'count': 12, 'total_duration_us': np.float64(890.515), 'mean_duration_us': np.float64(74.20958333333333), 'median_duration_us': np.float64(74.31), 'std_dev_duration_us': np.float64(0.7594008008877068), 'min_duration_us': np.float64(72.646), 'max_duration_us': np.float64(75.212)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x128x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB1024_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT4_8_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW4_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA4_VWB8_WSGRA0_WSGRB0_WS64_WG64_4_1', 'stream': 0, 'gpu_op_uid': 49066, 'count': 12, 'total_duration_us': np.float64(890.515), 'mean_duration_us': np.float64(74.20958333333333), 'median_duration_us': np.float64(74.31), 'std_dev_duration_us': np.float64(0.7594008008877068), 'min_duration_us': np.float64(72.646), 'max_duration_us': np.float64(75.212)}]</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -17632,7 +17632,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMBSK_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD0_NTM0_NEPBS0_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4', 'stream': 0, 'count': 1, 'total_duration_us': np.float64(9.261), 'mean_duration_us': np.float64(9.261), 'median_duration_us': np.float64(9.261), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(9.261), 'max_duration_us': np.float64(9.261)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMBSK_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD0_NTM0_NEPBS0_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4', 'stream': 0, 'gpu_op_uid': 49882, 'count': 1, 'total_duration_us': np.float64(9.261), 'mean_duration_us': np.float64(9.261), 'median_duration_us': np.float64(9.261), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(9.261), 'max_duration_us': np.float64(9.261)}]</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -18052,7 +18052,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>[{'name': 'SubTensorOpWithScalar1d', 'stream': 0, 'count': 1, 'total_duration_us': np.float64(16.396), 'mean_duration_us': np.float64(16.396), 'median_duration_us': np.float64(16.396), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(16.396), 'max_duration_us': np.float64(16.396)}, {'name': 'batched_transpose_256x4_half', 'stream': 0, 'count': 1, 'total_duration_us': np.float64(33.917), 'mean_duration_us': np.float64(33.917), 'median_duration_us': np.float64(33.917), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(33.917), 'max_duration_us': np.float64(33.917)}, {'name': 'batched_transpose_128x4_half', 'stream': 0, 'count': 1, 'total_duration_us': np.float64(4.891), 'mean_duration_us': np.float64(4.891), 'median_duration_us': np.float64(4.891), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(4.891), 'max_duration_us': np.float64(4.891)}, {'name': 'igemm_fwd_gtcx3_nhwc_bf16_bx0_ex1_bt256x64x8_wt64x16x4_ws1x1_wr2x2_ta1x1x8x1_1x8x1x32_tb1x1x2x1_1x8x1x32_me', 'stream': 0, 'count': 1, 'total_duration_us': np.float64(246.806), 'mean_duration_us': np.float64(246.806), 'median_duration_us': np.float64(246.806), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(246.806), 'max_duration_us': np.float64(246.806)}, {'name': 'batched_transpose_32x16_half', 'stream': 0, 'count': 1, 'total_duration_us': np.float64(32.032), 'mean_duration_us': np.float64(32.032), 'median_duration_us': np.float64(32.032), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(32.032), 'max_duration_us': np.float64(32.032)}, {'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 1, 'total_duration_us': np.float64(51.999), 'mean_duration_us': np.float64(51.999), 'median_duration_us': np.float64(51.999), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(51.999), 'max_duration_us': np.float64(51.999)}]</t>
+          <t>[{'name': 'SubTensorOpWithScalar1d', 'stream': 0, 'gpu_op_uid': 48988, 'count': 1, 'total_duration_us': np.float64(16.396), 'mean_duration_us': np.float64(16.396), 'median_duration_us': np.float64(16.396), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(16.396), 'max_duration_us': np.float64(16.396)}, {'name': 'batched_transpose_256x4_half', 'stream': 0, 'gpu_op_uid': 48990, 'count': 1, 'total_duration_us': np.float64(33.917), 'mean_duration_us': np.float64(33.917), 'median_duration_us': np.float64(33.917), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(33.917), 'max_duration_us': np.float64(33.917)}, {'name': 'batched_transpose_128x4_half', 'stream': 0, 'gpu_op_uid': 48992, 'count': 1, 'total_duration_us': np.float64(4.891), 'mean_duration_us': np.float64(4.891), 'median_duration_us': np.float64(4.891), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(4.891), 'max_duration_us': np.float64(4.891)}, {'name': 'igemm_fwd_gtcx3_nhwc_bf16_bx0_ex1_bt256x64x8_wt64x16x4_ws1x1_wr2x2_ta1x1x8x1_1x8x1x32_tb1x1x2x1_1x8x1x32_me', 'stream': 0, 'gpu_op_uid': 48994, 'count': 1, 'total_duration_us': np.float64(246.806), 'mean_duration_us': np.float64(246.806), 'median_duration_us': np.float64(246.806), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(246.806), 'max_duration_us': np.float64(246.806)}, {'name': 'batched_transpose_32x16_half', 'stream': 0, 'gpu_op_uid': 48996, 'count': 1, 'total_duration_us': np.float64(32.032), 'mean_duration_us': np.float64(32.032), 'median_duration_us': np.float64(32.032), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(32.032), 'max_duration_us': np.float64(32.032)}, {'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'gpu_op_uid': 48998, 'count': 1, 'total_duration_us': np.float64(51.999), 'mean_duration_us': np.float64(51.999), 'median_duration_us': np.float64(51.999), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(51.999), 'max_duration_us': np.float64(51.999)}]</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -18114,7 +18114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL8"/>
+  <dimension ref="A1:AJ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18125,185 +18125,175 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>param: shape_in1</t>
+          <t>param: op_shape</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>param: shape_in2</t>
+          <t>param: dtype_in_out</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>param: dtype_in1_in2_out</t>
+          <t>param: stride_input</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>param: stride_input1</t>
+          <t>param: stride_output</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>param: stride_input2</t>
+          <t>GFLOPS_first</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>param: stride_output</t>
+          <t>Data Moved (MB)_first</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>GFLOPS_first</t>
+          <t>FLOPS/Byte_first</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Data Moved (MB)_first</t>
+          <t>TB/s_mean</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>FLOPS/Byte_first</t>
+          <t>TB/s_median</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>TB/s_mean</t>
+          <t>TB/s_std</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>TB/s_median</t>
+          <t>TB/s_min</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>TB/s_std</t>
+          <t>TB/s_max</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>TB/s_min</t>
+          <t>TFLOPS/s_mean</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>TB/s_max</t>
+          <t>TFLOPS/s_median</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>TFLOPS/s_mean</t>
+          <t>TFLOPS/s_std</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>TFLOPS/s_median</t>
+          <t>TFLOPS/s_min</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>TFLOPS/s_std</t>
+          <t>TFLOPS/s_max</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>TFLOPS/s_min</t>
+          <t>process_name_first</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>TFLOPS/s_max</t>
+          <t>process_label_first</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>process_name_first</t>
+          <t>thread_name_first</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>process_label_first</t>
+          <t>Compute Spec</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>thread_name_first</t>
+          <t>kernel_details__summarize_kernel_stats</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Compute Spec</t>
+          <t>trunc_kernel_details</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>kernel_details__summarize_kernel_stats</t>
+          <t>Input Dims_first</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>trunc_kernel_details</t>
+          <t>Input type_first</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>Input Dims_first</t>
+          <t>Input Strides_first</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>Input type_first</t>
+          <t>Concrete Inputs_first</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>Input Strides_first</t>
+          <t>Kernel Time (µs)_mean</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>Concrete Inputs_first</t>
+          <t>Kernel Time (µs)_median</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>Kernel Time (µs)_mean</t>
+          <t>Kernel Time (µs)_std</t>
         </is>
       </c>
       <c r="AF1" t="inlineStr">
         <is>
-          <t>Kernel Time (µs)_median</t>
+          <t>Kernel Time (µs)_min</t>
         </is>
       </c>
       <c r="AG1" t="inlineStr">
         <is>
-          <t>Kernel Time (µs)_std</t>
+          <t>Kernel Time (µs)_max</t>
         </is>
       </c>
       <c r="AH1" t="inlineStr">
         <is>
-          <t>Kernel Time (µs)_min</t>
+          <t>Kernel Time (µs)_sum</t>
         </is>
       </c>
       <c r="AI1" t="inlineStr">
         <is>
-          <t>Kernel Time (µs)_max</t>
+          <t>name_count</t>
         </is>
       </c>
       <c r="AJ1" t="inlineStr">
-        <is>
-          <t>Kernel Time (µs)_sum</t>
-        </is>
-      </c>
-      <c r="AK1" t="inlineStr">
-        <is>
-          <t>name_count</t>
-        </is>
-      </c>
-      <c r="AL1" t="inlineStr">
         <is>
           <t>UID_first</t>
         </is>
@@ -18312,1005 +18302,1771 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>aten::mul</t>
+          <t>aten::copy_</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>(8, 12, 3137, 3137)</t>
+          <t>(8, 12, 64, 3137)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>()</t>
+          <t>('c10::BFloat16', 'c10::BFloat16')</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>('c10::BFloat16', 'double', None)</t>
+          <t>(2409216, 200768, 3137, 1)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>(118089228, 9840769, 3137, 1)</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>()</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>(7227648, 64, 1, 2304)</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0.019273728</v>
+      </c>
+      <c r="G2" t="n">
+        <v>73.5234375</v>
+      </c>
       <c r="H2" t="n">
-        <v>0.944713824</v>
+        <v>0.25</v>
       </c>
       <c r="I2" t="n">
-        <v>3603.797248840332</v>
+        <v>0.4846034771008995</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2499999994707392</v>
+        <v>0.4824393891763367</v>
       </c>
       <c r="K2" t="n">
-        <v>4.138162629285227</v>
+        <v>0.01494992388424028</v>
       </c>
       <c r="L2" t="n">
-        <v>4.126000450178768</v>
+        <v>0.4599275832842986</v>
       </c>
       <c r="M2" t="n">
-        <v>0.02832041716391857</v>
+        <v>0.5190177172874002</v>
       </c>
       <c r="N2" t="n">
-        <v>4.108375941528961</v>
+        <v>0.1211508692752249</v>
       </c>
       <c r="O2" t="n">
-        <v>4.205906817186887</v>
+        <v>0.1206098472940842</v>
       </c>
       <c r="P2" t="n">
-        <v>1.03454065513114</v>
+        <v>0.003737480971060071</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.031500110360962</v>
+        <v>0.1149818958210747</v>
       </c>
       <c r="R2" t="n">
-        <v>0.007080104275990777</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1.027093983207838</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.0514767020707</v>
+        <v>0.1297544293218501</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>python3</t>
+          <t>thread 13201 (python3)</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>vector_bf16</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>thread 13201 (python3)</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'gpu_op_uid': 49052, 'count': 12, 'total_duration_us': np.float64(1910.6989999999998), 'mean_duration_us': np.float64(159.22491666666664), 'median_duration_us': np.float64(159.806), 'std_dev_duration_us': np.float64(4.617114114147013), 'min_duration_us': np.float64(148.54), 'max_duration_us': np.float64(167.624)}]</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>vector_bf16</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(159.22)}]</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 12, 'total_duration_us': np.float64(10958.534), 'mean_duration_us': np.float64(913.2111666666666), 'median_duration_us': np.float64(915.864), 'std_dev_duration_us': np.float64(5.93463524340141), 'min_duration_us': np.float64(898.464), 'max_duration_us': np.float64(919.793)}]</t>
+          <t>[[8, 12, 64, 3137], [8, 12, 64, 3137], []]</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AU...', 'stream': 0, 'mean_duration_us': np.float64(913.21)}]</t>
+          <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>[[8, 12, 3137, 3137], []]</t>
+          <t>[[2409216, 200768, 3137, 1], [7227648, 64, 1, 2304], []]</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>['c10::BFloat16', 'double']</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>[[118089228, 9840769, 3137, 1], []]</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>['', '']</t>
-        </is>
+          <t>['', '', 'False']</t>
+        </is>
+      </c>
+      <c r="AC2" t="n">
+        <v>159.2248942057292</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>159.805908203125</v>
       </c>
       <c r="AE2" t="n">
-        <v>913.2111409505209</v>
+        <v>4.82242672625831</v>
       </c>
       <c r="AF2" t="n">
-        <v>915.864013671875</v>
+        <v>148.5400390625</v>
       </c>
       <c r="AG2" t="n">
-        <v>6.198513648286477</v>
+        <v>167.6240234375</v>
       </c>
       <c r="AH2" t="n">
-        <v>898.4638671875</v>
+        <v>1910.69873046875</v>
       </c>
       <c r="AI2" t="n">
-        <v>919.79296875</v>
+        <v>12</v>
       </c>
       <c r="AJ2" t="n">
-        <v>10958.53369140625</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>266</v>
+        <v>261</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>aten::add</t>
+          <t>aten::copy_</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>(1, 25089, 768)</t>
+          <t>(1, 128, 3, 224, 224)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>(1, 25089, 768)</t>
+          <t>('c10::BFloat16', 'c10::BFloat16')</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>('c10::BFloat16', 'c10::BFloat16', None)</t>
+          <t>(19267584, 150528, 50176, 224, 1)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>(19268352, 768, 1)</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>(19268352, 768, 1)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>(19267584, 150528, 50176, 224, 1)</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0.019267584</v>
+      </c>
+      <c r="G3" t="n">
+        <v>73.5</v>
+      </c>
       <c r="H3" t="n">
-        <v>0.019268352</v>
+        <v>0.25</v>
       </c>
       <c r="I3" t="n">
-        <v>110.25439453125</v>
+        <v>0.0707207963739921</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="K3" t="n">
-        <v>4.068091029454154</v>
-      </c>
+        <v>0.0707207963739921</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>4.087379526738395</v>
+        <v>0.0707207963739921</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2461091586957631</v>
+        <v>0.0707207963739921</v>
       </c>
       <c r="N3" t="n">
-        <v>3.503855171752449</v>
+        <v>0.01768019909349803</v>
       </c>
       <c r="O3" t="n">
-        <v>4.464064355964479</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0.6780151715756922</v>
-      </c>
+        <v>0.01768019909349803</v>
+      </c>
+      <c r="P3" t="inlineStr"/>
       <c r="Q3" t="n">
-        <v>0.6812299211230658</v>
+        <v>0.01768019909349803</v>
       </c>
       <c r="R3" t="n">
-        <v>0.04101819311596054</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0.5839758619587415</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0.7440107259940797</v>
+        <v>0.01768019909349803</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>python3</t>
+          <t>thread 13201 (python3)</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>vector_bf16</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>thread 13201 (python3)</t>
+          <t>[{'name': 'Memcpy HtoD (Host -&gt; Device)', 'stream': 0, 'gpu_op_uid': 48986, 'count': 1, 'total_duration_us': np.float64(1089.783), 'mean_duration_us': np.float64(1089.783), 'median_duration_us': np.float64(1089.783), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(1089.783), 'max_duration_us': np.float64(1089.783)}]</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>vector_bf16</t>
+          <t>[{'name': 'Memcpy HtoD (Host -&gt; Device)', 'stream': 0, 'mean_duration_us': np.float64(1089.78)}]</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 24, 'total_duration_us': np.float64(684.548), 'mean_duration_us': np.float64(28.522833333333335), 'median_duration_us': np.float64(28.2845), 'std_dev_duration_us': np.float64(1.7633981320797134), 'min_duration_us': np.float64(25.898), 'max_duration_us': np.float64(32.995)}]</t>
+          <t>[[1, 128, 3, 224, 224], [1, 128, 3, 224, 224], []]</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CU...', 'stream': 0, 'mean_duration_us': np.float64(28.52)}]</t>
+          <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>[[1, 25089, 768], [1, 25089, 768], []]</t>
+          <t>[[19267584, 150528, 50176, 224, 1], [19267584, 150528, 50176, 224, 1], []]</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>[[19268352, 768, 1], [19268352, 768, 1], []]</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>['', '', '1']</t>
-        </is>
-      </c>
-      <c r="AE3" t="n">
-        <v>28.52288818359375</v>
-      </c>
+          <t>['', '', 'False']</t>
+        </is>
+      </c>
+      <c r="AC3" t="n">
+        <v>1089.783203125</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1089.783203125</v>
+      </c>
+      <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="n">
-        <v>28.28466796875</v>
+        <v>1089.783203125</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.801307580797709</v>
+        <v>1089.783203125</v>
       </c>
       <c r="AH3" t="n">
-        <v>25.89794921875</v>
+        <v>1089.783203125</v>
       </c>
       <c r="AI3" t="n">
-        <v>32.9951171875</v>
+        <v>1</v>
       </c>
       <c r="AJ3" t="n">
-        <v>684.54931640625</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>331</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>aten::add</t>
+          <t>aten::copy_</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>(1, 25088, 768)</t>
+          <t>(3136, 12, 8, 64)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>(1, 25088, 768)</t>
+          <t>('c10::BFloat16', 'c10::BFloat16')</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>('c10::BFloat16', 'c10::BFloat16', None)</t>
+          <t>(6144, 512, 64, 1)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>(19268352, 768, 1)</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>(19267584, 768, 1)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>(18432, 64, 2304, 1)</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0.019267584</v>
+      </c>
+      <c r="G4" t="n">
+        <v>73.5</v>
+      </c>
       <c r="H4" t="n">
-        <v>0.019267584</v>
+        <v>0.25</v>
       </c>
       <c r="I4" t="n">
-        <v>110.25</v>
+        <v>2.600064317968634</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1666666666666667</v>
+        <v>2.566585810446347</v>
       </c>
       <c r="K4" t="n">
-        <v>4.228950328018581</v>
+        <v>0.1161834493060445</v>
       </c>
       <c r="L4" t="n">
-        <v>4.25961780389596</v>
+        <v>2.421156708307768</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2430675835275143</v>
+        <v>2.843811111615589</v>
       </c>
       <c r="N4" t="n">
-        <v>3.769344586894223</v>
+        <v>0.6500160794921584</v>
       </c>
       <c r="O4" t="n">
-        <v>4.628649922621258</v>
+        <v>0.6416464526115867</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7048250546697638</v>
+        <v>0.02904586232651114</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.7099363006493267</v>
+        <v>0.605289177076942</v>
       </c>
       <c r="R4" t="n">
-        <v>0.04051126392125243</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.628224097815704</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0.7714416537702098</v>
+        <v>0.7109527779038972</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>python3</t>
+          <t>thread 13201 (python3)</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>vector_bf16</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>thread 13201 (python3)</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'gpu_op_uid': 49018, 'count': 24, 'total_duration_us': np.float64(712.733), 'mean_duration_us': np.float64(29.697208333333332), 'median_duration_us': np.float64(30.0285), 'std_dev_duration_us': np.float64(1.2709403991784545), 'min_duration_us': np.float64(27.101), 'max_duration_us': np.float64(31.832)}]</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>vector_bf16</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(29.7)}]</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 12, 'total_duration_us': np.float64(329.064), 'mean_duration_us': np.float64(27.422), 'median_duration_us': np.float64(27.1415), 'std_dev_duration_us': np.float64(1.5525699125428567), 'min_duration_us': np.float64(24.976), 'max_duration_us': np.float64(30.67)}]</t>
+          <t>[[3136, 12, 8, 64], [3136, 12, 8, 64], []]</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CU...', 'stream': 0, 'mean_duration_us': np.float64(27.42)}]</t>
+          <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>[[1, 25088, 768], [1, 25088, 768], []]</t>
+          <t>[[6144, 512, 64, 1], [18432, 64, 2304, 1], []]</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>[[19268352, 768, 1], [19267584, 768, 1], []]</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>['', '', '1']</t>
-        </is>
+          <t>['', '', 'False']</t>
+        </is>
+      </c>
+      <c r="AC4" t="n">
+        <v>29.69724527994792</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>30.028564453125</v>
       </c>
       <c r="AE4" t="n">
-        <v>27.42195638020833</v>
+        <v>1.298277837881316</v>
       </c>
       <c r="AF4" t="n">
-        <v>27.141357421875</v>
+        <v>27.10107421875</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.62156079664857</v>
+        <v>31.83203125</v>
       </c>
       <c r="AH4" t="n">
-        <v>24.97607421875</v>
+        <v>712.73388671875</v>
       </c>
       <c r="AI4" t="n">
-        <v>30.669921875</v>
+        <v>24</v>
       </c>
       <c r="AJ4" t="n">
-        <v>329.0634765625</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>185</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>aten::add</t>
+          <t>aten::copy_</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>(196, 128, 768)</t>
+          <t>(8, 12, 3137, 64)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>(1, 128, 768)</t>
+          <t>('c10::BFloat16', 'c10::BFloat16')</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>('c10::BFloat16', 'c10::BFloat16', None)</t>
+          <t>(2409216, 200768, 64, 1)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>(768, 151296, 1)</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>(98304, 1, 128)</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>(7227648, 64, 2304, 1)</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0.019273728</v>
+      </c>
+      <c r="G5" t="n">
+        <v>73.5234375</v>
+      </c>
       <c r="H5" t="n">
-        <v>0.019267584</v>
+        <v>0.25</v>
       </c>
       <c r="I5" t="n">
-        <v>73.6875</v>
+        <v>2.688488535911089</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2493638676844784</v>
+        <v>2.616430812009449</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6345902796416455</v>
+        <v>0.133824819053682</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6345902796416455</v>
-      </c>
-      <c r="M5" t="inlineStr"/>
+        <v>2.517063827573014</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2.891765197362637</v>
+      </c>
       <c r="N5" t="n">
-        <v>0.6345902796416455</v>
+        <v>0.6721221339777723</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6345902796416455</v>
+        <v>0.6541077030023623</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1582438865264154</v>
+        <v>0.03345620476342049</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1582438865264154</v>
-      </c>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="n">
-        <v>0.1582438865264154</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.1582438865264154</v>
+        <v>0.6292659568932534</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.7229412993406593</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>python3</t>
+          <t>thread 13201 (python3)</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>vector_bf16</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>thread 13201 (python3)</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'gpu_op_uid': 49050, 'count': 24, 'total_duration_us': np.float64(689.8420000000001), 'mean_duration_us': np.float64(28.743416666666672), 'median_duration_us': np.float64(29.4665), 'std_dev_duration_us': np.float64(1.3861626563005591), 'min_duration_us': np.float64(26.66), 'max_duration_us': np.float64(30.629)}]</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>vector_bf16</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(28.74)}]</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 1, 'total_duration_us': np.float64(121.759), 'mean_duration_us': np.float64(121.759), 'median_duration_us': np.float64(121.759), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(121.759), 'max_duration_us': np.float64(121.759)}]</t>
+          <t>[[8, 12, 3137, 64], [8, 12, 3137, 64], []]</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(121.76)}]</t>
+          <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>[[196, 128, 768], [1, 128, 768], []]</t>
+          <t>[[2409216, 200768, 64, 1], [7227648, 64, 2304, 1], []]</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>[[768, 151296, 1], [98304, 1, 128], []]</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>['', '', '1']</t>
-        </is>
+          <t>['', '', 'False']</t>
+        </is>
+      </c>
+      <c r="AC5" t="n">
+        <v>28.74344889322917</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>29.466552734375</v>
       </c>
       <c r="AE5" t="n">
-        <v>121.7587890625</v>
+        <v>1.415932687354162</v>
       </c>
       <c r="AF5" t="n">
-        <v>121.7587890625</v>
-      </c>
-      <c r="AG5" t="inlineStr"/>
+        <v>26.66015625</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>30.62890625</v>
+      </c>
       <c r="AH5" t="n">
-        <v>121.7587890625</v>
+        <v>689.8427734375</v>
       </c>
       <c r="AI5" t="n">
-        <v>121.7587890625</v>
+        <v>24</v>
       </c>
       <c r="AJ5" t="n">
-        <v>121.7587890625</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>60</v>
+        <v>253</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>aten::mul</t>
+          <t>aten::copy_</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>(3136, 12, 8, 8)</t>
+          <t>(3136, 12, 64, 8)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>()</t>
+          <t>('c10::BFloat16', 'c10::BFloat16')</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>('c10::BFloat16', 'double', None)</t>
+          <t>(6144, 512, 8, 1)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>(768, 64, 8, 1)</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>()</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>(18432, 64, 1, 2304)</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0.019267584</v>
+      </c>
+      <c r="G6" t="n">
+        <v>73.5</v>
+      </c>
       <c r="H6" t="n">
-        <v>0.002408448</v>
+        <v>0.25</v>
       </c>
       <c r="I6" t="n">
-        <v>9.187507629394531</v>
+        <v>1.916837415450844</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2499997923976001</v>
+        <v>1.879122466595315</v>
       </c>
       <c r="K6" t="n">
-        <v>1.774385769640316</v>
+        <v>0.1331424422967764</v>
       </c>
       <c r="L6" t="n">
-        <v>1.74774405612562</v>
+        <v>1.815296700724554</v>
       </c>
       <c r="M6" t="n">
-        <v>0.07560839768275071</v>
+        <v>2.327269147592227</v>
       </c>
       <c r="N6" t="n">
-        <v>1.680437986542884</v>
+        <v>0.4792093538627109</v>
       </c>
       <c r="O6" t="n">
-        <v>1.922442015005359</v>
+        <v>0.4697806166488286</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4435960740433349</v>
+        <v>0.03328561057419409</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.4369356511955446</v>
+        <v>0.4538241751811386</v>
       </c>
       <c r="R6" t="n">
-        <v>0.01890208372420286</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.4201091477727621</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0.4806101046477639</v>
+        <v>0.5818172868980568</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>python3</t>
+          <t>thread 13201 (python3)</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>vector_bf16</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>thread 13201 (python3)</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'gpu_op_uid': 49020, 'count': 12, 'total_duration_us': np.float64(484.30300000000005), 'mean_duration_us': np.float64(40.358583333333335), 'median_duration_us': np.float64(41.013999999999996), 'std_dev_duration_us': np.float64(2.2839961127496595), 'min_duration_us': np.float64(33.116), 'max_duration_us': np.float64(42.456)}]</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>vector_bf16</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(40.36)}]</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 12, 'total_duration_us': np.float64(65.258), 'mean_duration_us': np.float64(5.438166666666667), 'median_duration_us': np.float64(5.5120000000000005), 'std_dev_duration_us': np.float64(0.21539724283802278), 'min_duration_us': np.float64(5.011), 'max_duration_us': np.float64(5.733)}]</t>
+          <t>[[3136, 12, 64, 8], [3136, 12, 64, 8], []]</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AU...', 'stream': 0, 'mean_duration_us': np.float64(5.44)}]</t>
+          <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>[[3136, 12, 8, 8], []]</t>
+          <t>[[6144, 512, 8, 1], [18432, 64, 1, 2304], []]</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>['c10::BFloat16', 'double']</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>[[768, 64, 8, 1], []]</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>['', '']</t>
-        </is>
+          <t>['', '', 'False']</t>
+        </is>
+      </c>
+      <c r="AC6" t="n">
+        <v>40.35868326822916</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>41.01416015625</v>
       </c>
       <c r="AE6" t="n">
-        <v>5.438151041666667</v>
+        <v>2.385508087539597</v>
       </c>
       <c r="AF6" t="n">
-        <v>5.51220703125</v>
+        <v>33.1162109375</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.2249131712685538</v>
+        <v>42.4560546875</v>
       </c>
       <c r="AH6" t="n">
-        <v>5.01123046875</v>
+        <v>484.30419921875</v>
       </c>
       <c r="AI6" t="n">
-        <v>5.73291015625</v>
+        <v>12</v>
       </c>
       <c r="AJ6" t="n">
-        <v>65.2578125</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>128</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>aten::add_</t>
+          <t>aten::copy_</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>(128, 768, 14, 14)</t>
+          <t>(1, 224, 14, 8, 768)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>(1, 768, 1, 1)</t>
+          <t>('c10::BFloat16', 'c10::BFloat16')</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>('c10::BFloat16', 'c10::BFloat16', None)</t>
+          <t>(19267584, 86016, 6144, 768, 1)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>(150528, 196, 14, 1)</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>(768, 1, 1, 1)</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+          <t>(19273728, 10752, 768, 2409216, 1)</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0.019267584</v>
+      </c>
+      <c r="G7" t="n">
+        <v>73.5</v>
+      </c>
       <c r="H7" t="n">
-        <v>0.019267584</v>
+        <v>0.25</v>
       </c>
       <c r="I7" t="n">
-        <v>73.50146484375</v>
+        <v>2.141015223109931</v>
       </c>
       <c r="J7" t="n">
-        <v>0.249995017637563</v>
+        <v>2.144365618848129</v>
       </c>
       <c r="K7" t="n">
-        <v>1.482179220012395</v>
+        <v>0.03972926180663784</v>
       </c>
       <c r="L7" t="n">
-        <v>1.482179220012395</v>
-      </c>
-      <c r="M7" t="inlineStr"/>
+        <v>2.049418285936871</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2.186998394502023</v>
+      </c>
       <c r="N7" t="n">
-        <v>1.482179220012395</v>
+        <v>0.5352538057774827</v>
       </c>
       <c r="O7" t="n">
-        <v>1.482179220012395</v>
+        <v>0.5360914047120322</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3705374202490281</v>
+        <v>0.00993231545165946</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.3705374202490281</v>
-      </c>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="n">
-        <v>0.3705374202490281</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0.3705374202490281</v>
+        <v>0.5123545714842178</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.5467495986255058</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>python3</t>
+          <t>thread 13201 (python3)</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>vector_bf16</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>thread 13201 (python3)</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'gpu_op_uid': 49070, 'count': 12, 'total_duration_us': np.float64(432.103), 'mean_duration_us': np.float64(36.008583333333334), 'median_duration_us': np.float64(35.941500000000005), 'std_dev_duration_us': np.float64(0.6513263977368714), 'min_duration_us': np.float64(35.24), 'max_duration_us': np.float64(37.606)}]</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>vector_bf16</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(36.01)}]</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 1, 'total_duration_us': np.float64(51.999), 'mean_duration_us': np.float64(51.999), 'median_duration_us': np.float64(51.999), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(51.999), 'max_duration_us': np.float64(51.999)}]</t>
+          <t>[[1, 224, 14, 8, 768], [1, 224, 14, 8, 768], []]</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(52.0)}]</t>
+          <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>[[128, 768, 14, 14], [1, 768, 1, 1], []]</t>
+          <t>[[19267584, 86016, 6144, 768, 1], [19273728, 10752, 768, 2409216, 1], []]</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>[[150528, 196, 14, 1], [768, 1, 1, 1], []]</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>['', '', '1']</t>
-        </is>
+          <t>['', '', 'False']</t>
+        </is>
+      </c>
+      <c r="AC7" t="n">
+        <v>36.0086669921875</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>35.94140625</v>
       </c>
       <c r="AE7" t="n">
-        <v>51.9990234375</v>
+        <v>0.6802631081377949</v>
       </c>
       <c r="AF7" t="n">
-        <v>51.9990234375</v>
-      </c>
-      <c r="AG7" t="inlineStr"/>
+        <v>35.240234375</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>37.60595703125</v>
+      </c>
       <c r="AH7" t="n">
-        <v>51.9990234375</v>
+        <v>432.10400390625</v>
       </c>
       <c r="AI7" t="n">
-        <v>51.9990234375</v>
+        <v>12</v>
       </c>
       <c r="AJ7" t="n">
-        <v>51.9990234375</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>21</v>
+        <v>327</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>aten::add</t>
+          <t>aten::copy_</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>(128, 197, 768)</t>
+          <t>(8, 3137, 12, 64)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>(1, 197, 768)</t>
+          <t>('c10::BFloat16', 'c10::BFloat16')</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>('c10::BFloat16', 'c10::BFloat16', None)</t>
+          <t>(2409216, 768, 64, 1)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>(151296, 768, 1)</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>(151296, 768, 1)</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>(2409216, 64, 200768, 1)</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>0.019273728</v>
+      </c>
+      <c r="G8" t="n">
+        <v>73.5234375</v>
+      </c>
       <c r="H8" t="n">
-        <v>0.019365888</v>
+        <v>0.25</v>
       </c>
       <c r="I8" t="n">
-        <v>74.16357421875</v>
+        <v>2.568255426812742</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2490272373540856</v>
+        <v>2.567453054586311</v>
       </c>
       <c r="K8" t="n">
-        <v>2.610645885847294</v>
+        <v>0.02630836954782855</v>
       </c>
       <c r="L8" t="n">
-        <v>2.610645885847294</v>
-      </c>
-      <c r="M8" t="inlineStr"/>
+        <v>2.53025399875002</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2.616331606283556</v>
+      </c>
       <c r="N8" t="n">
-        <v>2.610645885847294</v>
+        <v>0.6420638567031854</v>
       </c>
       <c r="O8" t="n">
-        <v>2.610645885847294</v>
+        <v>0.6418632636465779</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6501219326623612</v>
+        <v>0.006577092386957137</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.6501219326623612</v>
-      </c>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="n">
-        <v>0.6501219326623612</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0.6501219326623612</v>
+        <v>0.632563499687505</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.6540829015708889</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
+          <t>thread 13201 (python3)</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>vector_bf16</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'gpu_op_uid': 49064, 'count': 12, 'total_duration_us': np.float64(360.25499999999994), 'mean_duration_us': np.float64(30.021249999999995), 'median_duration_us': np.float64(30.028), 'std_dev_duration_us': np.float64(0.29395269602437757), 'min_duration_us': np.float64(29.467), 'max_duration_us': np.float64(30.469)}]</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(30.02)}]</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>[[8, 3137, 12, 64], [8, 3137, 12, 64], []]</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>[[2409216, 768, 64, 1], [2409216, 64, 200768, 1], []]</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>['', '', 'False']</t>
+        </is>
+      </c>
+      <c r="AC8" t="n">
+        <v>30.02128092447917</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>30.02783203125</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.3071000383842391</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>29.466796875</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>30.46923828125</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>360.25537109375</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>aten::copy_</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>(3136, 8, 12, 64)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>('c10::BFloat16', 'c10::BFloat16')</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>(6144, 768, 64, 1)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>(6144, 64, 512, 1)</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>0.019267584</v>
+      </c>
+      <c r="G9" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.575966288579531</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.613723043668635</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.1103564994053667</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.261642758676028</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2.655317667816227</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.6439915721448827</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.6534307609171588</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.02758912485134168</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.565410689669007</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.6638294169540568</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
           <t>python3</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>thread 13201 (python3)</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>vector_bf16</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 1, 'total_duration_us': np.float64(29.788), 'mean_duration_us': np.float64(29.788), 'median_duration_us': np.float64(29.788), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(29.788), 'max_duration_us': np.float64(29.788)}]</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(29.79)}]</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>[[128, 197, 768], [1, 197, 768], []]</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'gpu_op_uid': 49032, 'count': 12, 'total_duration_us': np.float64(359.694), 'mean_duration_us': np.float64(29.974500000000003), 'median_duration_us': np.float64(29.487000000000002), 'std_dev_duration_us': np.float64(1.353853789496241), 'min_duration_us': np.float64(29.025), 'max_duration_us': np.float64(34.077)}]</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(29.97)}]</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>[[3136, 8, 12, 64], [3136, 8, 12, 64], []]</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
         <is>
           <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>[[151296, 768, 1], [151296, 768, 1], []]</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>['', '', '1']</t>
-        </is>
-      </c>
-      <c r="AE8" t="n">
-        <v>29.7880859375</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>29.7880859375</v>
-      </c>
-      <c r="AG8" t="inlineStr"/>
-      <c r="AH8" t="n">
-        <v>29.7880859375</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>29.7880859375</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>29.7880859375</v>
-      </c>
-      <c r="AK8" t="n">
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>[[6144, 768, 64, 1], [6144, 64, 512, 1], []]</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>['', '', 'False']</t>
+        </is>
+      </c>
+      <c r="AC9" t="n">
+        <v>29.9744873046875</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>29.48681640625</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.414092988509887</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>29.02490234375</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>34.0771484375</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>359.69384765625</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>aten::copy_</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>(1, 8, 1, 1, 1, 768)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>('c10::BFloat16', 'c10::BFloat16')</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>(6144, 768, 768, 6144, 768, 1)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>(0, 0, 19268352, 19268352, 768, 1)</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>6.144e-06</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.0234375</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.005009545718958677</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.004944169792305976</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.0003222248414490439</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.004540928184770841</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.00572992349726776</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.001252386429739669</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.001236042448076494</v>
+      </c>
+      <c r="P10" t="n">
+        <v>8.055621036226098e-05</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.00113523204619271</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.00143248087431694</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>thread 13201 (python3)</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>vector_bf16</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'gpu_op_uid': 49042, 'count': 12, 'total_duration_us': np.float64(59.084), 'mean_duration_us': np.float64(4.923666666666667), 'median_duration_us': np.float64(4.9704999999999995), 'std_dev_duration_us': np.float64(0.2903455795350698), 'min_duration_us': np.float64(4.289), 'max_duration_us': np.float64(5.412)}]</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(4.92)}]</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>[[1, 8, 1, 1, 1, 768], [1, 8, 1, 1, 1, 768], []]</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>[[6144, 768, 768, 6144, 768, 1], [0, 0, 19268352, 19268352, 768, 1], []]</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>['', '', 'False']</t>
+        </is>
+      </c>
+      <c r="AC10" t="n">
+        <v>4.923665364583333</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>4.970703125</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.3032574531977062</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>4.2890625</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>5.412109375</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>59.083984375</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>aten::copy_</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>(1, 196, 128, 768)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>('c10::BFloat16', 'c10::BFloat16')</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>(19267584, 98304, 768, 1)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>(150528, 768, 150528, 1)</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>0.019267584</v>
+      </c>
+      <c r="G11" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.486923301947438</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.486923301947438</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="n">
+        <v>2.486923301947438</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2.486923301947438</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.6217308254868595</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.6217308254868595</v>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="n">
+        <v>0.6217308254868595</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.6217308254868595</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>thread 13201 (python3)</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>vector_bf16</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'gpu_op_uid': 49010, 'count': 1, 'total_duration_us': np.float64(30.99), 'mean_duration_us': np.float64(30.99), 'median_duration_us': np.float64(30.99), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(30.99), 'max_duration_us': np.float64(30.99)}]</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(30.99)}]</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>[[1, 196, 128, 768], [1, 196, 128, 768], []]</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>[[19267584, 98304, 768, 1], [150528, 768, 150528, 1], []]</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>['', '', 'False']</t>
+        </is>
+      </c>
+      <c r="AC11" t="n">
+        <v>30.990234375</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>30.990234375</v>
+      </c>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="n">
+        <v>30.990234375</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>30.990234375</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>30.990234375</v>
+      </c>
+      <c r="AI11" t="n">
         <v>1</v>
       </c>
-      <c r="AL8" t="n">
-        <v>29</v>
+      <c r="AJ11" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>aten::copy_</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>(1, 768, 8)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>('c10::BFloat16', 'c10::BFloat16')</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>(6144, 8, 1)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>(6144, 1, 768)</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>6.144e-06</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.0234375</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.003784334436090226</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.003784334436090226</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="n">
+        <v>0.003784334436090226</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.003784334436090226</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.0009460836090225565</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.0009460836090225565</v>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="n">
+        <v>0.0009460836090225565</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.0009460836090225565</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>thread 13201 (python3)</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>vector_bf16</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'gpu_op_uid': 49004, 'count': 1, 'total_duration_us': np.float64(6.494), 'mean_duration_us': np.float64(6.494), 'median_duration_us': np.float64(6.494), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(6.494), 'max_duration_us': np.float64(6.494)}]</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(6.49)}]</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>[[1, 768, 8], [1, 768, 8], []]</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>[[6144, 8, 1], [6144, 1, 768], []]</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>['', '', 'False']</t>
+        </is>
+      </c>
+      <c r="AC12" t="n">
+        <v>6.494140625</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>6.494140625</v>
+      </c>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="n">
+        <v>6.494140625</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>6.494140625</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>6.494140625</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>aten::copy_</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>(1, 400)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>('c10::BFloat16', 'c10::BFloat16')</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>(400, 1)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>(400, 1)</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>4e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.00152587890625</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.000380227430958459</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.000380227430958459</v>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="n">
+        <v>0.000380227430958459</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.000380227430958459</v>
+      </c>
+      <c r="N13" t="n">
+        <v>9.505685773961475e-05</v>
+      </c>
+      <c r="O13" t="n">
+        <v>9.505685773961475e-05</v>
+      </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="n">
+        <v>9.505685773961475e-05</v>
+      </c>
+      <c r="R13" t="n">
+        <v>9.505685773961475e-05</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>thread 13201 (python3)</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>vector_bf16</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'gpu_op_uid': 49884, 'count': 1, 'total_duration_us': np.float64(4.208), 'mean_duration_us': np.float64(4.208), 'median_duration_us': np.float64(4.208), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(4.208), 'max_duration_us': np.float64(4.208)}]</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'mean_duration_us': np.float64(4.21)}]</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>[[1, 400], [1, 400], []]</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>[[400, 1], [400, 1], []]</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>['', '', 'False']</t>
+        </is>
+      </c>
+      <c r="AC13" t="n">
+        <v>4.2080078125</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>4.2080078125</v>
+      </c>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="n">
+        <v>4.2080078125</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>4.2080078125</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>4.2080078125</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>3582</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>aten::copy_</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>(1, 128, 3, 224, 224)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>('c10::BFloat16', 'float')</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>(19267584, 150528, 50176, 224, 1)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>(19267584, 150528, 50176, 224, 1)</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0.019267584</v>
+      </c>
+      <c r="G14" t="n">
+        <v>110.25</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>thread 13201 (python3)</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>vector_bf16</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>[[1, 128, 3, 224, 224], [1, 128, 3, 224, 224], []]</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>['c10::BFloat16', 'float', 'Scalar']</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>[[19267584, 150528, 50176, 224, 1], [19267584, 150528, 50176, 224, 1], []]</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>['', '', 'False']</t>
+        </is>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -19324,7 +20080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ14"/>
+  <dimension ref="A1:AL8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19335,175 +20091,185 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>param: op_shape</t>
+          <t>param: shape_in1</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>param: dtype_in_out</t>
+          <t>param: shape_in2</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>param: stride_input</t>
+          <t>param: dtype_in1_in2_out</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>param: stride_input1</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>param: stride_input2</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>param: stride_output</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>GFLOPS_first</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Data Moved (MB)_first</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>FLOPS/Byte_first</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>TB/s_mean</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>TB/s_median</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>TB/s_std</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>TB/s_min</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>TB/s_max</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>TFLOPS/s_mean</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>TFLOPS/s_median</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>TFLOPS/s_std</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>TFLOPS/s_min</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>TFLOPS/s_max</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>process_name_first</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>process_label_first</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>thread_name_first</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Compute Spec</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>kernel_details__summarize_kernel_stats</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>trunc_kernel_details</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Input Dims_first</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Input type_first</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Input Strides_first</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Concrete Inputs_first</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_mean</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_median</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_std</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_min</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_max</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_sum</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>name_count</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>UID_first</t>
         </is>
@@ -19512,1771 +20278,1005 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>aten::copy_</t>
+          <t>aten::mul</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>(8, 12, 64, 3137)</t>
+          <t>(8, 12, 3137, 3137)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>('c10::BFloat16', 'c10::BFloat16')</t>
+          <t>()</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>(2409216, 200768, 3137, 1)</t>
+          <t>('c10::BFloat16', 'double', None)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>(7227648, 64, 1, 2304)</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>0.019273728</v>
-      </c>
-      <c r="G2" t="n">
-        <v>73.5234375</v>
-      </c>
+          <t>(118089228, 9840769, 3137, 1)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>()</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.25</v>
+        <v>0.944713824</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4846034771008995</v>
+        <v>3603.797248840332</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4824393891763367</v>
+        <v>0.2499999994707392</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01494992388424028</v>
+        <v>4.138162629285227</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4599275832842986</v>
+        <v>4.126000450178768</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5190177172874002</v>
+        <v>0.02832041716391857</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1211508692752249</v>
+        <v>4.108375941528961</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1206098472940842</v>
+        <v>4.205906817186887</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003737480971060071</v>
+        <v>1.03454065513114</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1149818958210747</v>
+        <v>1.031500110360962</v>
       </c>
       <c r="R2" t="n">
-        <v>0.1297544293218501</v>
-      </c>
-      <c r="S2" t="inlineStr">
+        <v>0.007080104275990777</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.027093983207838</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.0514767020707</v>
+      </c>
+      <c r="U2" t="inlineStr">
         <is>
           <t>python3</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>thread 13201 (python3)</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>vector_bf16</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 12, 'total_duration_us': np.float64(1910.6989999999998), 'mean_duration_us': np.float64(159.22491666666664), 'median_duration_us': np.float64(159.806), 'std_dev_duration_us': np.float64(4.617114114147013), 'min_duration_us': np.float64(148.54), 'max_duration_us': np.float64(167.624)}]</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(159.22)}]</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>[[8, 12, 64, 3137], [8, 12, 64, 3137], []]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'gpu_op_uid': 49056, 'count': 12, 'total_duration_us': np.float64(10958.534), 'mean_duration_us': np.float64(913.2111666666666), 'median_duration_us': np.float64(915.864), 'std_dev_duration_us': np.float64(5.93463524340141), 'min_duration_us': np.float64(898.464), 'max_duration_us': np.float64(919.793)}]</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AU...', 'stream': 0, 'mean_duration_us': np.float64(913.21)}]</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>[[2409216, 200768, 3137, 1], [7227648, 64, 1, 2304], []]</t>
+          <t>[[8, 12, 3137, 3137], []]</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>['', '', 'False']</t>
-        </is>
-      </c>
-      <c r="AC2" t="n">
-        <v>159.2248942057292</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>159.805908203125</v>
+          <t>['c10::BFloat16', 'double']</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>[[118089228, 9840769, 3137, 1], []]</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>['', '']</t>
+        </is>
       </c>
       <c r="AE2" t="n">
-        <v>4.82242672625831</v>
+        <v>913.2111409505209</v>
       </c>
       <c r="AF2" t="n">
-        <v>148.5400390625</v>
+        <v>915.864013671875</v>
       </c>
       <c r="AG2" t="n">
-        <v>167.6240234375</v>
+        <v>6.198513648286477</v>
       </c>
       <c r="AH2" t="n">
-        <v>1910.69873046875</v>
+        <v>898.4638671875</v>
       </c>
       <c r="AI2" t="n">
+        <v>919.79296875</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>10958.53369140625</v>
+      </c>
+      <c r="AK2" t="n">
         <v>12</v>
       </c>
-      <c r="AJ2" t="n">
-        <v>261</v>
+      <c r="AL2" t="n">
+        <v>266</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>aten::copy_</t>
+          <t>aten::add</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>(1, 128, 3, 224, 224)</t>
+          <t>(1, 25089, 768)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>('c10::BFloat16', 'c10::BFloat16')</t>
+          <t>(1, 25089, 768)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>(19267584, 150528, 50176, 224, 1)</t>
+          <t>('c10::BFloat16', 'c10::BFloat16', None)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>(19267584, 150528, 50176, 224, 1)</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>0.019267584</v>
-      </c>
-      <c r="G3" t="n">
-        <v>73.5</v>
-      </c>
+          <t>(19268352, 768, 1)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>(19268352, 768, 1)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.25</v>
+        <v>0.019268352</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0707207963739921</v>
+        <v>110.25439453125</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0707207963739921</v>
-      </c>
-      <c r="K3" t="inlineStr"/>
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="K3" t="n">
+        <v>4.068091029454154</v>
+      </c>
       <c r="L3" t="n">
-        <v>0.0707207963739921</v>
+        <v>4.087379526738395</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0707207963739921</v>
+        <v>0.2461091586957631</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01768019909349803</v>
+        <v>3.503855171752449</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01768019909349803</v>
-      </c>
-      <c r="P3" t="inlineStr"/>
+        <v>4.464064355964479</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.6780151715756922</v>
+      </c>
       <c r="Q3" t="n">
-        <v>0.01768019909349803</v>
+        <v>0.6812299211230658</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01768019909349803</v>
-      </c>
-      <c r="S3" t="inlineStr">
+        <v>0.04101819311596054</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.5839758619587415</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.7440107259940797</v>
+      </c>
+      <c r="U3" t="inlineStr">
         <is>
           <t>python3</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>thread 13201 (python3)</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>vector_bf16</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>[{'name': 'Memcpy HtoD (Host -&gt; Device)', 'stream': 0, 'count': 1, 'total_duration_us': np.float64(1089.783), 'mean_duration_us': np.float64(1089.783), 'median_duration_us': np.float64(1089.783), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(1089.783), 'max_duration_us': np.float64(1089.783)}]</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>[{'name': 'Memcpy HtoD (Host -&gt; Device)', 'stream': 0, 'mean_duration_us': np.float64(1089.78)}]</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>[[1, 128, 3, 224, 224], [1, 128, 3, 224, 224], []]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'gpu_op_uid': 49076, 'count': 24, 'total_duration_us': np.float64(684.548), 'mean_duration_us': np.float64(28.522833333333335), 'median_duration_us': np.float64(28.2845), 'std_dev_duration_us': np.float64(1.7633981320797134), 'min_duration_us': np.float64(25.898), 'max_duration_us': np.float64(32.995)}]</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CU...', 'stream': 0, 'mean_duration_us': np.float64(28.52)}]</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>[[1, 25089, 768], [1, 25089, 768], []]</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
           <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>[[19267584, 150528, 50176, 224, 1], [19267584, 150528, 50176, 224, 1], []]</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>['', '', 'False']</t>
-        </is>
-      </c>
-      <c r="AC3" t="n">
-        <v>1089.783203125</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1089.783203125</v>
-      </c>
-      <c r="AE3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>[[19268352, 768, 1], [19268352, 768, 1], []]</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>['', '', '1']</t>
+        </is>
+      </c>
+      <c r="AE3" t="n">
+        <v>28.52288818359375</v>
+      </c>
       <c r="AF3" t="n">
-        <v>1089.783203125</v>
+        <v>28.28466796875</v>
       </c>
       <c r="AG3" t="n">
-        <v>1089.783203125</v>
+        <v>1.801307580797709</v>
       </c>
       <c r="AH3" t="n">
-        <v>1089.783203125</v>
+        <v>25.89794921875</v>
       </c>
       <c r="AI3" t="n">
-        <v>1</v>
+        <v>32.9951171875</v>
       </c>
       <c r="AJ3" t="n">
-        <v>9</v>
+        <v>684.54931640625</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>331</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>aten::copy_</t>
+          <t>aten::add</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>(3136, 12, 8, 64)</t>
+          <t>(1, 25088, 768)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>('c10::BFloat16', 'c10::BFloat16')</t>
+          <t>(1, 25088, 768)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>(6144, 512, 64, 1)</t>
+          <t>('c10::BFloat16', 'c10::BFloat16', None)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>(18432, 64, 2304, 1)</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
+          <t>(19268352, 768, 1)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>(19267584, 768, 1)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="n">
         <v>0.019267584</v>
       </c>
-      <c r="G4" t="n">
-        <v>73.5</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.25</v>
-      </c>
       <c r="I4" t="n">
-        <v>2.600064317968634</v>
+        <v>110.25</v>
       </c>
       <c r="J4" t="n">
-        <v>2.566585810446347</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1161834493060445</v>
+        <v>4.228950328018581</v>
       </c>
       <c r="L4" t="n">
-        <v>2.421156708307768</v>
+        <v>4.25961780389596</v>
       </c>
       <c r="M4" t="n">
-        <v>2.843811111615589</v>
+        <v>0.2430675835275143</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6500160794921584</v>
+        <v>3.769344586894223</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6416464526115867</v>
+        <v>4.628649922621258</v>
       </c>
       <c r="P4" t="n">
-        <v>0.02904586232651114</v>
+        <v>0.7048250546697638</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.605289177076942</v>
+        <v>0.7099363006493267</v>
       </c>
       <c r="R4" t="n">
-        <v>0.7109527779038972</v>
-      </c>
-      <c r="S4" t="inlineStr">
+        <v>0.04051126392125243</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.628224097815704</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.7714416537702098</v>
+      </c>
+      <c r="U4" t="inlineStr">
         <is>
           <t>python3</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>thread 13201 (python3)</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>vector_bf16</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 24, 'total_duration_us': np.float64(712.733), 'mean_duration_us': np.float64(29.697208333333332), 'median_duration_us': np.float64(30.0285), 'std_dev_duration_us': np.float64(1.2709403991784545), 'min_duration_us': np.float64(27.101), 'max_duration_us': np.float64(31.832)}]</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(29.7)}]</t>
-        </is>
-      </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>[[3136, 12, 8, 64], [3136, 12, 8, 64], []]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'gpu_op_uid': 49038, 'count': 12, 'total_duration_us': np.float64(329.064), 'mean_duration_us': np.float64(27.422), 'median_duration_us': np.float64(27.1415), 'std_dev_duration_us': np.float64(1.5525699125428567), 'min_duration_us': np.float64(24.976), 'max_duration_us': np.float64(30.67)}]</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CU...', 'stream': 0, 'mean_duration_us': np.float64(27.42)}]</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>[[1, 25088, 768], [1, 25088, 768], []]</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
           <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>[[6144, 512, 64, 1], [18432, 64, 2304, 1], []]</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>['', '', 'False']</t>
-        </is>
-      </c>
-      <c r="AC4" t="n">
-        <v>29.69724527994792</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>30.028564453125</v>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>[[19268352, 768, 1], [19267584, 768, 1], []]</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>['', '', '1']</t>
+        </is>
       </c>
       <c r="AE4" t="n">
-        <v>1.298277837881316</v>
+        <v>27.42195638020833</v>
       </c>
       <c r="AF4" t="n">
-        <v>27.10107421875</v>
+        <v>27.141357421875</v>
       </c>
       <c r="AG4" t="n">
-        <v>31.83203125</v>
+        <v>1.62156079664857</v>
       </c>
       <c r="AH4" t="n">
-        <v>712.73388671875</v>
+        <v>24.97607421875</v>
       </c>
       <c r="AI4" t="n">
-        <v>24</v>
+        <v>30.669921875</v>
       </c>
       <c r="AJ4" t="n">
-        <v>115</v>
+        <v>329.0634765625</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>185</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>aten::copy_</t>
+          <t>aten::add</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>(8, 12, 3137, 64)</t>
+          <t>(196, 128, 768)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>('c10::BFloat16', 'c10::BFloat16')</t>
+          <t>(1, 128, 768)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>(2409216, 200768, 64, 1)</t>
+          <t>('c10::BFloat16', 'c10::BFloat16', None)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>(7227648, 64, 2304, 1)</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>0.019273728</v>
-      </c>
-      <c r="G5" t="n">
-        <v>73.5234375</v>
-      </c>
+          <t>(768, 151296, 1)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>(98304, 1, 128)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>0.25</v>
+        <v>0.019267584</v>
       </c>
       <c r="I5" t="n">
-        <v>2.688488535911089</v>
+        <v>73.6875</v>
       </c>
       <c r="J5" t="n">
-        <v>2.616430812009449</v>
+        <v>0.2493638676844784</v>
       </c>
       <c r="K5" t="n">
-        <v>0.133824819053682</v>
+        <v>0.6345902796416455</v>
       </c>
       <c r="L5" t="n">
-        <v>2.517063827573014</v>
-      </c>
-      <c r="M5" t="n">
-        <v>2.891765197362637</v>
-      </c>
+        <v>0.6345902796416455</v>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>0.6721221339777723</v>
+        <v>0.6345902796416455</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6541077030023623</v>
+        <v>0.6345902796416455</v>
       </c>
       <c r="P5" t="n">
-        <v>0.03345620476342049</v>
+        <v>0.1582438865264154</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.6292659568932534</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.7229412993406593</v>
-      </c>
-      <c r="S5" t="inlineStr">
+        <v>0.1582438865264154</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="n">
+        <v>0.1582438865264154</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.1582438865264154</v>
+      </c>
+      <c r="U5" t="inlineStr">
         <is>
           <t>python3</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>thread 13201 (python3)</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>vector_bf16</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 24, 'total_duration_us': np.float64(689.8420000000001), 'mean_duration_us': np.float64(28.743416666666672), 'median_duration_us': np.float64(29.4665), 'std_dev_duration_us': np.float64(1.3861626563005591), 'min_duration_us': np.float64(26.66), 'max_duration_us': np.float64(30.629)}]</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(28.74)}]</t>
-        </is>
-      </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>[[8, 12, 3137, 64], [8, 12, 3137, 64], []]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'gpu_op_uid': 49008, 'count': 1, 'total_duration_us': np.float64(121.759), 'mean_duration_us': np.float64(121.759), 'median_duration_us': np.float64(121.759), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(121.759), 'max_duration_us': np.float64(121.759)}]</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(121.76)}]</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>[[196, 128, 768], [1, 128, 768], []]</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
           <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>[[2409216, 200768, 64, 1], [7227648, 64, 2304, 1], []]</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>['', '', 'False']</t>
-        </is>
-      </c>
-      <c r="AC5" t="n">
-        <v>28.74344889322917</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>29.466552734375</v>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>[[768, 151296, 1], [98304, 1, 128], []]</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>['', '', '1']</t>
+        </is>
       </c>
       <c r="AE5" t="n">
-        <v>1.415932687354162</v>
+        <v>121.7587890625</v>
       </c>
       <c r="AF5" t="n">
-        <v>26.66015625</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>30.62890625</v>
-      </c>
+        <v>121.7587890625</v>
+      </c>
+      <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="n">
-        <v>689.8427734375</v>
+        <v>121.7587890625</v>
       </c>
       <c r="AI5" t="n">
-        <v>24</v>
+        <v>121.7587890625</v>
       </c>
       <c r="AJ5" t="n">
-        <v>253</v>
+        <v>121.7587890625</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>aten::copy_</t>
+          <t>aten::mul</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>(3136, 12, 64, 8)</t>
+          <t>(3136, 12, 8, 8)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>('c10::BFloat16', 'c10::BFloat16')</t>
+          <t>()</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>(6144, 512, 8, 1)</t>
+          <t>('c10::BFloat16', 'double', None)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>(18432, 64, 1, 2304)</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>0.019267584</v>
-      </c>
-      <c r="G6" t="n">
-        <v>73.5</v>
-      </c>
+          <t>(768, 64, 8, 1)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>()</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>0.25</v>
+        <v>0.002408448</v>
       </c>
       <c r="I6" t="n">
-        <v>1.916837415450844</v>
+        <v>9.187507629394531</v>
       </c>
       <c r="J6" t="n">
-        <v>1.879122466595315</v>
+        <v>0.2499997923976001</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1331424422967764</v>
+        <v>1.774385769640316</v>
       </c>
       <c r="L6" t="n">
-        <v>1.815296700724554</v>
+        <v>1.74774405612562</v>
       </c>
       <c r="M6" t="n">
-        <v>2.327269147592227</v>
+        <v>0.07560839768275071</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4792093538627109</v>
+        <v>1.680437986542884</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4697806166488286</v>
+        <v>1.922442015005359</v>
       </c>
       <c r="P6" t="n">
-        <v>0.03328561057419409</v>
+        <v>0.4435960740433349</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.4538241751811386</v>
+        <v>0.4369356511955446</v>
       </c>
       <c r="R6" t="n">
-        <v>0.5818172868980568</v>
-      </c>
-      <c r="S6" t="inlineStr">
+        <v>0.01890208372420286</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.4201091477727621</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.4806101046477639</v>
+      </c>
+      <c r="U6" t="inlineStr">
         <is>
           <t>python3</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>thread 13201 (python3)</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>vector_bf16</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 12, 'total_duration_us': np.float64(484.30300000000005), 'mean_duration_us': np.float64(40.358583333333335), 'median_duration_us': np.float64(41.013999999999996), 'std_dev_duration_us': np.float64(2.2839961127496595), 'min_duration_us': np.float64(33.116), 'max_duration_us': np.float64(42.456)}]</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(40.36)}]</t>
-        </is>
-      </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>[[3136, 12, 64, 8], [3136, 12, 64, 8], []]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'gpu_op_uid': 49024, 'count': 12, 'total_duration_us': np.float64(65.258), 'mean_duration_us': np.float64(5.438166666666667), 'median_duration_us': np.float64(5.5120000000000005), 'std_dev_duration_us': np.float64(0.21539724283802278), 'min_duration_us': np.float64(5.011), 'max_duration_us': np.float64(5.733)}]</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AU...', 'stream': 0, 'mean_duration_us': np.float64(5.44)}]</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>[[6144, 512, 8, 1], [18432, 64, 1, 2304], []]</t>
+          <t>[[3136, 12, 8, 8], []]</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>['', '', 'False']</t>
-        </is>
-      </c>
-      <c r="AC6" t="n">
-        <v>40.35868326822916</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>41.01416015625</v>
+          <t>['c10::BFloat16', 'double']</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>[[768, 64, 8, 1], []]</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>['', '']</t>
+        </is>
       </c>
       <c r="AE6" t="n">
-        <v>2.385508087539597</v>
+        <v>5.438151041666667</v>
       </c>
       <c r="AF6" t="n">
-        <v>33.1162109375</v>
+        <v>5.51220703125</v>
       </c>
       <c r="AG6" t="n">
-        <v>42.4560546875</v>
+        <v>0.2249131712685538</v>
       </c>
       <c r="AH6" t="n">
-        <v>484.30419921875</v>
+        <v>5.01123046875</v>
       </c>
       <c r="AI6" t="n">
+        <v>5.73291015625</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>65.2578125</v>
+      </c>
+      <c r="AK6" t="n">
         <v>12</v>
       </c>
-      <c r="AJ6" t="n">
-        <v>123</v>
+      <c r="AL6" t="n">
+        <v>128</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>aten::copy_</t>
+          <t>aten::add_</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>(1, 224, 14, 8, 768)</t>
+          <t>(128, 768, 14, 14)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>('c10::BFloat16', 'c10::BFloat16')</t>
+          <t>(1, 768, 1, 1)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>(19267584, 86016, 6144, 768, 1)</t>
+          <t>('c10::BFloat16', 'c10::BFloat16', None)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>(19273728, 10752, 768, 2409216, 1)</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
+          <t>(150528, 196, 14, 1)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>(768, 1, 1, 1)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="n">
         <v>0.019267584</v>
       </c>
-      <c r="G7" t="n">
-        <v>73.5</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.25</v>
-      </c>
       <c r="I7" t="n">
-        <v>2.141015223109931</v>
+        <v>73.50146484375</v>
       </c>
       <c r="J7" t="n">
-        <v>2.144365618848129</v>
+        <v>0.249995017637563</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03972926180663784</v>
+        <v>1.482179220012395</v>
       </c>
       <c r="L7" t="n">
-        <v>2.049418285936871</v>
-      </c>
-      <c r="M7" t="n">
-        <v>2.186998394502023</v>
-      </c>
+        <v>1.482179220012395</v>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>0.5352538057774827</v>
+        <v>1.482179220012395</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5360914047120322</v>
+        <v>1.482179220012395</v>
       </c>
       <c r="P7" t="n">
-        <v>0.00993231545165946</v>
+        <v>0.3705374202490281</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.5123545714842178</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0.5467495986255058</v>
-      </c>
-      <c r="S7" t="inlineStr">
+        <v>0.3705374202490281</v>
+      </c>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="n">
+        <v>0.3705374202490281</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.3705374202490281</v>
+      </c>
+      <c r="U7" t="inlineStr">
         <is>
           <t>python3</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>thread 13201 (python3)</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>vector_bf16</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 12, 'total_duration_us': np.float64(432.103), 'mean_duration_us': np.float64(36.008583333333334), 'median_duration_us': np.float64(35.941500000000005), 'std_dev_duration_us': np.float64(0.6513263977368714), 'min_duration_us': np.float64(35.24), 'max_duration_us': np.float64(37.606)}]</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(36.01)}]</t>
-        </is>
-      </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>[[1, 224, 14, 8, 768], [1, 224, 14, 8, 768], []]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'gpu_op_uid': 48998, 'count': 1, 'total_duration_us': np.float64(51.999), 'mean_duration_us': np.float64(51.999), 'median_duration_us': np.float64(51.999), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(51.999), 'max_duration_us': np.float64(51.999)}]</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(52.0)}]</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>[[128, 768, 14, 14], [1, 768, 1, 1], []]</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
           <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>[[19267584, 86016, 6144, 768, 1], [19273728, 10752, 768, 2409216, 1], []]</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>['', '', 'False']</t>
-        </is>
-      </c>
-      <c r="AC7" t="n">
-        <v>36.0086669921875</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>35.94140625</v>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>[[150528, 196, 14, 1], [768, 1, 1, 1], []]</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>['', '', '1']</t>
+        </is>
       </c>
       <c r="AE7" t="n">
-        <v>0.6802631081377949</v>
+        <v>51.9990234375</v>
       </c>
       <c r="AF7" t="n">
-        <v>35.240234375</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>37.60595703125</v>
-      </c>
+        <v>51.9990234375</v>
+      </c>
+      <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="n">
-        <v>432.10400390625</v>
+        <v>51.9990234375</v>
       </c>
       <c r="AI7" t="n">
-        <v>12</v>
+        <v>51.9990234375</v>
       </c>
       <c r="AJ7" t="n">
-        <v>327</v>
+        <v>51.9990234375</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>aten::copy_</t>
+          <t>aten::add</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>(8, 3137, 12, 64)</t>
+          <t>(128, 197, 768)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>('c10::BFloat16', 'c10::BFloat16')</t>
+          <t>(1, 197, 768)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>(2409216, 768, 64, 1)</t>
+          <t>('c10::BFloat16', 'c10::BFloat16', None)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>(2409216, 64, 200768, 1)</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>0.019273728</v>
-      </c>
-      <c r="G8" t="n">
-        <v>73.5234375</v>
-      </c>
+          <t>(151296, 768, 1)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>(151296, 768, 1)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>0.25</v>
+        <v>0.019365888</v>
       </c>
       <c r="I8" t="n">
-        <v>2.568255426812742</v>
+        <v>74.16357421875</v>
       </c>
       <c r="J8" t="n">
-        <v>2.567453054586311</v>
+        <v>0.2490272373540856</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02630836954782855</v>
+        <v>2.610645885847294</v>
       </c>
       <c r="L8" t="n">
-        <v>2.53025399875002</v>
-      </c>
-      <c r="M8" t="n">
-        <v>2.616331606283556</v>
-      </c>
+        <v>2.610645885847294</v>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="n">
-        <v>0.6420638567031854</v>
+        <v>2.610645885847294</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6418632636465779</v>
+        <v>2.610645885847294</v>
       </c>
       <c r="P8" t="n">
-        <v>0.006577092386957137</v>
+        <v>0.6501219326623612</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.632563499687505</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.6540829015708889</v>
-      </c>
-      <c r="S8" t="inlineStr">
+        <v>0.6501219326623612</v>
+      </c>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="n">
+        <v>0.6501219326623612</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.6501219326623612</v>
+      </c>
+      <c r="U8" t="inlineStr">
         <is>
           <t>python3</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>thread 13201 (python3)</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>vector_bf16</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 12, 'total_duration_us': np.float64(360.25499999999994), 'mean_duration_us': np.float64(30.021249999999995), 'median_duration_us': np.float64(30.028), 'std_dev_duration_us': np.float64(0.29395269602437757), 'min_duration_us': np.float64(29.467), 'max_duration_us': np.float64(30.469)}]</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(30.02)}]</t>
-        </is>
-      </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>[[8, 3137, 12, 64], [8, 3137, 12, 64], []]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'gpu_op_uid': 49002, 'count': 1, 'total_duration_us': np.float64(29.788), 'mean_duration_us': np.float64(29.788), 'median_duration_us': np.float64(29.788), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(29.788), 'max_duration_us': np.float64(29.788)}]</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(29.79)}]</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>[[128, 197, 768], [1, 197, 768], []]</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
           <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>[[2409216, 768, 64, 1], [2409216, 64, 200768, 1], []]</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>['', '', 'False']</t>
-        </is>
-      </c>
-      <c r="AC8" t="n">
-        <v>30.02128092447917</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>30.02783203125</v>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>[[151296, 768, 1], [151296, 768, 1], []]</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>['', '', '1']</t>
+        </is>
       </c>
       <c r="AE8" t="n">
-        <v>0.3071000383842391</v>
+        <v>29.7880859375</v>
       </c>
       <c r="AF8" t="n">
-        <v>29.466796875</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>30.46923828125</v>
-      </c>
+        <v>29.7880859375</v>
+      </c>
+      <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="n">
-        <v>360.25537109375</v>
+        <v>29.7880859375</v>
       </c>
       <c r="AI8" t="n">
-        <v>12</v>
+        <v>29.7880859375</v>
       </c>
       <c r="AJ8" t="n">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>aten::copy_</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>(3136, 8, 12, 64)</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>('c10::BFloat16', 'c10::BFloat16')</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>(6144, 768, 64, 1)</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>(6144, 64, 512, 1)</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>0.019267584</v>
-      </c>
-      <c r="G9" t="n">
-        <v>73.5</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2.575966288579531</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2.613723043668635</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.1103564994053667</v>
-      </c>
-      <c r="L9" t="n">
-        <v>2.261642758676028</v>
-      </c>
-      <c r="M9" t="n">
-        <v>2.655317667816227</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.6439915721448827</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.6534307609171588</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0.02758912485134168</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0.565410689669007</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0.6638294169540568</v>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>python3</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>CPU</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>thread 13201 (python3)</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>vector_bf16</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 12, 'total_duration_us': np.float64(359.694), 'mean_duration_us': np.float64(29.974500000000003), 'median_duration_us': np.float64(29.487000000000002), 'std_dev_duration_us': np.float64(1.353853789496241), 'min_duration_us': np.float64(29.025), 'max_duration_us': np.float64(34.077)}]</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(29.97)}]</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>[[3136, 8, 12, 64], [3136, 8, 12, 64], []]</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>[[6144, 768, 64, 1], [6144, 64, 512, 1], []]</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>['', '', 'False']</t>
-        </is>
-      </c>
-      <c r="AC9" t="n">
-        <v>29.9744873046875</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>29.48681640625</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.414092988509887</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>29.02490234375</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>34.0771484375</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>359.69384765625</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>aten::copy_</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>(1, 8, 1, 1, 1, 768)</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>('c10::BFloat16', 'c10::BFloat16')</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>(6144, 768, 768, 6144, 768, 1)</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>(0, 0, 19268352, 19268352, 768, 1)</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>6.144e-06</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.0234375</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.005009545718958677</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.004944169792305976</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0.0003222248414490439</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0.004540928184770841</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0.00572992349726776</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0.001252386429739669</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0.001236042448076494</v>
-      </c>
-      <c r="P10" t="n">
-        <v>8.055621036226098e-05</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0.00113523204619271</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0.00143248087431694</v>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>python3</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>CPU</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>thread 13201 (python3)</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>vector_bf16</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 12, 'total_duration_us': np.float64(59.084), 'mean_duration_us': np.float64(4.923666666666667), 'median_duration_us': np.float64(4.9704999999999995), 'std_dev_duration_us': np.float64(0.2903455795350698), 'min_duration_us': np.float64(4.289), 'max_duration_us': np.float64(5.412)}]</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(4.92)}]</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>[[1, 8, 1, 1, 1, 768], [1, 8, 1, 1, 1, 768], []]</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>[[6144, 768, 768, 6144, 768, 1], [0, 0, 19268352, 19268352, 768, 1], []]</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>['', '', 'False']</t>
-        </is>
-      </c>
-      <c r="AC10" t="n">
-        <v>4.923665364583333</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>4.970703125</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0.3032574531977062</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>4.2890625</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>5.412109375</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>59.083984375</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>12</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>aten::copy_</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>(1, 196, 128, 768)</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>('c10::BFloat16', 'c10::BFloat16')</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>(19267584, 98304, 768, 1)</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>(150528, 768, 150528, 1)</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>0.019267584</v>
-      </c>
-      <c r="G11" t="n">
-        <v>73.5</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I11" t="n">
-        <v>2.486923301947438</v>
-      </c>
-      <c r="J11" t="n">
-        <v>2.486923301947438</v>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="n">
-        <v>2.486923301947438</v>
-      </c>
-      <c r="M11" t="n">
-        <v>2.486923301947438</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.6217308254868595</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0.6217308254868595</v>
-      </c>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="n">
-        <v>0.6217308254868595</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0.6217308254868595</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>python3</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>CPU</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>thread 13201 (python3)</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>vector_bf16</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 1, 'total_duration_us': np.float64(30.99), 'mean_duration_us': np.float64(30.99), 'median_duration_us': np.float64(30.99), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(30.99), 'max_duration_us': np.float64(30.99)}]</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(30.99)}]</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>[[1, 196, 128, 768], [1, 196, 128, 768], []]</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>[[19267584, 98304, 768, 1], [150528, 768, 150528, 1], []]</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>['', '', 'False']</t>
-        </is>
-      </c>
-      <c r="AC11" t="n">
-        <v>30.990234375</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>30.990234375</v>
-      </c>
-      <c r="AE11" t="inlineStr"/>
-      <c r="AF11" t="n">
-        <v>30.990234375</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>30.990234375</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>30.990234375</v>
-      </c>
-      <c r="AI11" t="n">
+        <v>29.7880859375</v>
+      </c>
+      <c r="AK8" t="n">
         <v>1</v>
       </c>
-      <c r="AJ11" t="n">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>aten::copy_</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>(1, 768, 8)</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>('c10::BFloat16', 'c10::BFloat16')</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>(6144, 8, 1)</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>(6144, 1, 768)</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>6.144e-06</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.0234375</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.003784334436090226</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.003784334436090226</v>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="n">
-        <v>0.003784334436090226</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0.003784334436090226</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0.0009460836090225565</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0.0009460836090225565</v>
-      </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="n">
-        <v>0.0009460836090225565</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0.0009460836090225565</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>python3</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>CPU</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>thread 13201 (python3)</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>vector_bf16</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 1, 'total_duration_us': np.float64(6.494), 'mean_duration_us': np.float64(6.494), 'median_duration_us': np.float64(6.494), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(6.494), 'max_duration_us': np.float64(6.494)}]</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(6.49)}]</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>[[1, 768, 8], [1, 768, 8], []]</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>[[6144, 8, 1], [6144, 1, 768], []]</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>['', '', 'False']</t>
-        </is>
-      </c>
-      <c r="AC12" t="n">
-        <v>6.494140625</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>6.494140625</v>
-      </c>
-      <c r="AE12" t="inlineStr"/>
-      <c r="AF12" t="n">
-        <v>6.494140625</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>6.494140625</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>6.494140625</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>aten::copy_</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>(1, 400)</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>('c10::BFloat16', 'c10::BFloat16')</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>(400, 1)</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>(400, 1)</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>4e-07</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.00152587890625</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.000380227430958459</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.000380227430958459</v>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="n">
-        <v>0.000380227430958459</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0.000380227430958459</v>
-      </c>
-      <c r="N13" t="n">
-        <v>9.505685773961475e-05</v>
-      </c>
-      <c r="O13" t="n">
-        <v>9.505685773961475e-05</v>
-      </c>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="n">
-        <v>9.505685773961475e-05</v>
-      </c>
-      <c r="R13" t="n">
-        <v>9.505685773961475e-05</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>python3</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>CPU</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>thread 13201 (python3)</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>vector_bf16</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'count': 1, 'total_duration_us': np.float64(4.208), 'mean_duration_us': np.float64(4.208), 'median_duration_us': np.float64(4.208), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(4.208), 'max_duration_us': np.float64(4.208)}]</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'mean_duration_us': np.float64(4.21)}]</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>[[1, 400], [1, 400], []]</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>[[400, 1], [400, 1], []]</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>['', '', 'False']</t>
-        </is>
-      </c>
-      <c r="AC13" t="n">
-        <v>4.2080078125</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>4.2080078125</v>
-      </c>
-      <c r="AE13" t="inlineStr"/>
-      <c r="AF13" t="n">
-        <v>4.2080078125</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>4.2080078125</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>4.2080078125</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>3582</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>aten::copy_</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>(1, 128, 3, 224, 224)</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>('c10::BFloat16', 'float')</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>(19267584, 150528, 50176, 224, 1)</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>(19267584, 150528, 50176, 224, 1)</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>0.019267584</v>
-      </c>
-      <c r="G14" t="n">
-        <v>110.25</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>python3</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>CPU</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>thread 13201 (python3)</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>vector_bf16</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>[[1, 128, 3, 224, 224], [1, 128, 3, 224, 224], []]</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>['c10::BFloat16', 'float', 'Scalar']</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>[[19267584, 150528, 50176, 224, 1], [19267584, 150528, 50176, 224, 1], []]</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>['', '', 'False']</t>
-        </is>
-      </c>
-      <c r="AC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="inlineStr"/>
-      <c r="AF14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>5</v>
+      <c r="AL8" t="n">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
